--- a/research/traditional_assets/database/data/ireland/ireland_machinery.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_machinery.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09875159672360384</v>
+        <v>0.09866753222769933</v>
       </c>
       <c r="C2">
-        <v>141.0943599896461</v>
+        <v>139.8678410489424</v>
       </c>
       <c r="D2">
-        <v>124.194359989646</v>
+        <v>124.3918410489424</v>
       </c>
       <c r="E2">
-        <v>-41.29999999999999</v>
+        <v>-39.87599999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.424</v>
       </c>
       <c r="G2">
         <v>16.9</v>
@@ -1579,28 +1579,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07162719999999999</v>
       </c>
       <c r="N2">
-        <v>12.52666666666667</v>
+        <v>12.45503946666667</v>
       </c>
       <c r="O2">
-        <v>1.565833333333333</v>
+        <v>1.556879933333333</v>
       </c>
       <c r="P2">
-        <v>10.96083333333333</v>
+        <v>10.89815953333333</v>
       </c>
       <c r="Q2">
-        <v>13.90083333333333</v>
+        <v>13.83815953333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09875159672360384</v>
+        <v>0.09921960326030235</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.041247497398554</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>174.8870075427585</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09866753222769933</v>
+        <v>0.09858346773179483</v>
       </c>
       <c r="C3">
-        <v>139.8678410489424</v>
+        <v>138.6419511364711</v>
       </c>
       <c r="D3">
-        <v>124.3918410489424</v>
+        <v>124.5899511364711</v>
       </c>
       <c r="E3">
-        <v>-39.87599999999999</v>
+        <v>-38.45199999999999</v>
       </c>
       <c r="F3">
-        <v>1.424</v>
+        <v>2.847999999999999</v>
       </c>
       <c r="G3">
         <v>16.9</v>
@@ -1661,28 +1661,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M3">
-        <v>0.07162719999999999</v>
+        <v>0.1432544</v>
       </c>
       <c r="N3">
-        <v>12.45503946666667</v>
+        <v>12.38341226666667</v>
       </c>
       <c r="O3">
-        <v>1.556879933333333</v>
+        <v>1.547926533333333</v>
       </c>
       <c r="P3">
-        <v>10.89815953333333</v>
+        <v>10.83548573333333</v>
       </c>
       <c r="Q3">
-        <v>13.83815953333333</v>
+        <v>13.77548573333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09921960326030235</v>
+        <v>0.09969716095081105</v>
       </c>
       <c r="T3">
-        <v>1.041247497398554</v>
+        <v>1.05055598566423</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>174.8870075427585</v>
+        <v>87.44350377137923</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09858346773179483</v>
+        <v>0.09849940323589031</v>
       </c>
       <c r="C4">
-        <v>138.6419511364711</v>
+        <v>137.4166932624526</v>
       </c>
       <c r="D4">
-        <v>124.5899511364711</v>
+        <v>124.7886932624526</v>
       </c>
       <c r="E4">
-        <v>-38.45199999999999</v>
+        <v>-37.02799999999999</v>
       </c>
       <c r="F4">
-        <v>2.847999999999999</v>
+        <v>4.271999999999999</v>
       </c>
       <c r="G4">
         <v>16.9</v>
@@ -1743,28 +1743,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M4">
-        <v>0.1432544</v>
+        <v>0.2148816</v>
       </c>
       <c r="N4">
-        <v>12.38341226666667</v>
+        <v>12.31178506666667</v>
       </c>
       <c r="O4">
-        <v>1.547926533333333</v>
+        <v>1.538973133333333</v>
       </c>
       <c r="P4">
-        <v>10.83548573333333</v>
+        <v>10.77281193333333</v>
       </c>
       <c r="Q4">
-        <v>13.77548573333333</v>
+        <v>13.71281193333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09969716095081105</v>
+        <v>0.1001845651916395</v>
       </c>
       <c r="T4">
-        <v>1.05055598566423</v>
+        <v>1.060056401523013</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>87.44350377137923</v>
+        <v>58.2956691809195</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09849940323589031</v>
+        <v>0.0984153387399858</v>
       </c>
       <c r="C5">
-        <v>137.4166932624526</v>
+        <v>136.1920704563453</v>
       </c>
       <c r="D5">
-        <v>124.7886932624526</v>
+        <v>124.9880704563453</v>
       </c>
       <c r="E5">
-        <v>-37.02799999999999</v>
+        <v>-35.60399999999999</v>
       </c>
       <c r="F5">
-        <v>4.271999999999999</v>
+        <v>5.695999999999999</v>
       </c>
       <c r="G5">
         <v>16.9</v>
@@ -1825,28 +1825,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M5">
-        <v>0.2148816</v>
+        <v>0.2865088</v>
       </c>
       <c r="N5">
-        <v>12.31178506666667</v>
+        <v>12.24015786666667</v>
       </c>
       <c r="O5">
-        <v>1.538973133333333</v>
+        <v>1.530019733333333</v>
       </c>
       <c r="P5">
-        <v>10.77281193333333</v>
+        <v>10.71013813333333</v>
       </c>
       <c r="Q5">
-        <v>13.71281193333333</v>
+        <v>13.65013813333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1001845651916395</v>
+        <v>0.1006821236874852</v>
       </c>
       <c r="T5">
-        <v>1.060056401523013</v>
+        <v>1.069754742712188</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.2956691809195</v>
+        <v>43.72175188568961</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0984153387399858</v>
+        <v>0.09833127424408129</v>
       </c>
       <c r="C6">
-        <v>136.1920704563453</v>
+        <v>134.9680857669994</v>
       </c>
       <c r="D6">
-        <v>124.9880704563453</v>
+        <v>125.1880857669994</v>
       </c>
       <c r="E6">
-        <v>-35.60399999999999</v>
+        <v>-34.17999999999999</v>
       </c>
       <c r="F6">
-        <v>5.695999999999999</v>
+        <v>7.119999999999999</v>
       </c>
       <c r="G6">
         <v>16.9</v>
@@ -1907,28 +1907,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M6">
-        <v>0.2865088</v>
+        <v>0.358136</v>
       </c>
       <c r="N6">
-        <v>12.24015786666667</v>
+        <v>12.16853066666667</v>
       </c>
       <c r="O6">
-        <v>1.530019733333333</v>
+        <v>1.521066333333333</v>
       </c>
       <c r="P6">
-        <v>10.71013813333333</v>
+        <v>10.64746433333333</v>
       </c>
       <c r="Q6">
-        <v>13.65013813333333</v>
+        <v>13.58746433333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1006821236874852</v>
+        <v>0.101190157099033</v>
       </c>
       <c r="T6">
-        <v>1.069754742712188</v>
+        <v>1.079657259505345</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.72175188568961</v>
+        <v>34.97740150855169</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09833127424408129</v>
+        <v>0.0982472097481768</v>
       </c>
       <c r="C7">
-        <v>134.9680857669994</v>
+        <v>133.7447422628127</v>
       </c>
       <c r="D7">
-        <v>125.1880857669994</v>
+        <v>125.3887422628127</v>
       </c>
       <c r="E7">
-        <v>-34.17999999999999</v>
+        <v>-32.75599999999999</v>
       </c>
       <c r="F7">
-        <v>7.119999999999999</v>
+        <v>8.543999999999999</v>
       </c>
       <c r="G7">
         <v>16.9</v>
@@ -1989,28 +1989,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M7">
-        <v>0.358136</v>
+        <v>0.4297631999999999</v>
       </c>
       <c r="N7">
-        <v>12.16853066666667</v>
+        <v>12.09690346666667</v>
       </c>
       <c r="O7">
-        <v>1.521066333333333</v>
+        <v>1.512112933333333</v>
       </c>
       <c r="P7">
-        <v>10.64746433333333</v>
+        <v>10.58479053333333</v>
       </c>
       <c r="Q7">
-        <v>13.58746433333333</v>
+        <v>13.52479053333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.101190157099033</v>
+        <v>0.101708999732103</v>
       </c>
       <c r="T7">
-        <v>1.079657259505345</v>
+        <v>1.089770468145165</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.97740150855169</v>
+        <v>29.14783459045974</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0982472097481768</v>
+        <v>0.09816314525227231</v>
       </c>
       <c r="C8">
-        <v>133.7447422628127</v>
+        <v>132.5220430318868</v>
       </c>
       <c r="D8">
-        <v>125.3887422628127</v>
+        <v>125.5900430318868</v>
       </c>
       <c r="E8">
-        <v>-32.75599999999999</v>
+        <v>-31.33199999999999</v>
       </c>
       <c r="F8">
-        <v>8.543999999999999</v>
+        <v>9.967999999999998</v>
       </c>
       <c r="G8">
         <v>16.9</v>
@@ -2071,28 +2071,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M8">
-        <v>0.4297631999999999</v>
+        <v>0.5013903999999999</v>
       </c>
       <c r="N8">
-        <v>12.09690346666667</v>
+        <v>12.02527626666667</v>
       </c>
       <c r="O8">
-        <v>1.512112933333333</v>
+        <v>1.503159533333333</v>
       </c>
       <c r="P8">
-        <v>10.58479053333333</v>
+        <v>10.52211673333333</v>
       </c>
       <c r="Q8">
-        <v>13.52479053333333</v>
+        <v>13.46211673333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.101708999732103</v>
+        <v>0.1022390002712605</v>
       </c>
       <c r="T8">
-        <v>1.089770468145165</v>
+        <v>1.10010116514283</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.14783459045974</v>
+        <v>24.98385822039407</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09816314525227229</v>
+        <v>0.0980790807563678</v>
       </c>
       <c r="C9">
-        <v>132.5220430318868</v>
+        <v>131.2999911821862</v>
       </c>
       <c r="D9">
-        <v>125.5900430318868</v>
+        <v>125.7919911821862</v>
       </c>
       <c r="E9">
-        <v>-31.33199999999999</v>
+        <v>-29.90799999999999</v>
       </c>
       <c r="F9">
-        <v>9.968</v>
+        <v>11.392</v>
       </c>
       <c r="G9">
         <v>16.9</v>
@@ -2153,28 +2153,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M9">
-        <v>0.5013904</v>
+        <v>0.5730175999999999</v>
       </c>
       <c r="N9">
-        <v>12.02527626666667</v>
+        <v>11.95364906666667</v>
       </c>
       <c r="O9">
-        <v>1.503159533333333</v>
+        <v>1.494206133333333</v>
       </c>
       <c r="P9">
-        <v>10.52211673333333</v>
+        <v>10.45944293333333</v>
       </c>
       <c r="Q9">
-        <v>13.46211673333333</v>
+        <v>13.39944293333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1022390002712605</v>
+        <v>0.1027805225612693</v>
       </c>
       <c r="T9">
-        <v>1.10010116514283</v>
+        <v>1.11065644251001</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.98385822039406</v>
+        <v>21.86087594284481</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0980790807563678</v>
+        <v>0.09799501626046328</v>
       </c>
       <c r="C10">
-        <v>131.2999911821862</v>
+        <v>130.0785898416978</v>
       </c>
       <c r="D10">
-        <v>125.7919911821862</v>
+        <v>125.9945898416978</v>
       </c>
       <c r="E10">
-        <v>-29.90799999999999</v>
+        <v>-28.48399999999999</v>
       </c>
       <c r="F10">
-        <v>11.392</v>
+        <v>12.816</v>
       </c>
       <c r="G10">
         <v>16.9</v>
@@ -2235,28 +2235,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M10">
-        <v>0.5730175999999999</v>
+        <v>0.6446447999999998</v>
       </c>
       <c r="N10">
-        <v>11.95364906666667</v>
+        <v>11.88202186666667</v>
       </c>
       <c r="O10">
-        <v>1.494206133333333</v>
+        <v>1.485252733333333</v>
       </c>
       <c r="P10">
-        <v>10.45944293333333</v>
+        <v>10.39676913333333</v>
       </c>
       <c r="Q10">
-        <v>13.39944293333333</v>
+        <v>13.33676913333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1027805225612693</v>
+        <v>0.1033339464400695</v>
       </c>
       <c r="T10">
-        <v>1.11065644251001</v>
+        <v>1.12144370399515</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.86087594284481</v>
+        <v>19.43188972697316</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09799501626046328</v>
+        <v>0.09791095176455879</v>
       </c>
       <c r="C11">
-        <v>130.0785898416978</v>
+        <v>128.8578421585925</v>
       </c>
       <c r="D11">
-        <v>125.9945898416978</v>
+        <v>126.1978421585925</v>
       </c>
       <c r="E11">
-        <v>-28.48399999999999</v>
+        <v>-27.06</v>
       </c>
       <c r="F11">
-        <v>12.816</v>
+        <v>14.24</v>
       </c>
       <c r="G11">
         <v>16.9</v>
@@ -2317,28 +2317,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M11">
-        <v>0.6446447999999998</v>
+        <v>0.7162719999999998</v>
       </c>
       <c r="N11">
-        <v>11.88202186666667</v>
+        <v>11.81039466666667</v>
       </c>
       <c r="O11">
-        <v>1.485252733333333</v>
+        <v>1.476299333333333</v>
       </c>
       <c r="P11">
-        <v>10.39676913333333</v>
+        <v>10.33409533333333</v>
       </c>
       <c r="Q11">
-        <v>13.33676913333333</v>
+        <v>13.27409533333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1033339464400695</v>
+        <v>0.1038996686272875</v>
       </c>
       <c r="T11">
-        <v>1.12144370399515</v>
+        <v>1.132470682402182</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.43188972697316</v>
+        <v>17.48870075427585</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09791095176455879</v>
+        <v>0.09782688726865428</v>
       </c>
       <c r="C12">
-        <v>128.8578421585925</v>
+        <v>127.6377513013886</v>
       </c>
       <c r="D12">
-        <v>126.1978421585925</v>
+        <v>126.4017513013886</v>
       </c>
       <c r="E12">
-        <v>-27.05999999999999</v>
+        <v>-25.63599999999999</v>
       </c>
       <c r="F12">
-        <v>14.24</v>
+        <v>15.664</v>
       </c>
       <c r="G12">
         <v>16.9</v>
@@ -2399,28 +2399,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M12">
-        <v>0.7162719999999999</v>
+        <v>0.7878991999999999</v>
       </c>
       <c r="N12">
-        <v>11.81039466666667</v>
+        <v>11.73876746666667</v>
       </c>
       <c r="O12">
-        <v>1.476299333333333</v>
+        <v>1.467345933333333</v>
       </c>
       <c r="P12">
-        <v>10.33409533333333</v>
+        <v>10.27142153333333</v>
       </c>
       <c r="Q12">
-        <v>13.27409533333333</v>
+        <v>13.21142153333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1038996686272875</v>
+        <v>0.1044781036726453</v>
       </c>
       <c r="T12">
-        <v>1.132470682402182</v>
+        <v>1.143745458076788</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.48870075427585</v>
+        <v>15.8988188675235</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09782688726865428</v>
+        <v>0.09774282277274977</v>
       </c>
       <c r="C13">
-        <v>127.6377513013886</v>
+        <v>126.4183204591158</v>
       </c>
       <c r="D13">
-        <v>126.4017513013886</v>
+        <v>126.6063204591158</v>
       </c>
       <c r="E13">
-        <v>-25.63599999999999</v>
+        <v>-24.21199999999999</v>
       </c>
       <c r="F13">
-        <v>15.664</v>
+        <v>17.088</v>
       </c>
       <c r="G13">
         <v>16.9</v>
@@ -2481,28 +2481,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M13">
-        <v>0.7878991999999999</v>
+        <v>0.8595263999999998</v>
       </c>
       <c r="N13">
-        <v>11.73876746666667</v>
+        <v>11.66714026666667</v>
       </c>
       <c r="O13">
-        <v>1.467345933333333</v>
+        <v>1.458392533333333</v>
       </c>
       <c r="P13">
-        <v>10.27142153333333</v>
+        <v>10.20874773333333</v>
       </c>
       <c r="Q13">
-        <v>13.21142153333333</v>
+        <v>13.14874773333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1044781036726453</v>
+        <v>0.1050696849690338</v>
       </c>
       <c r="T13">
-        <v>1.143745458076788</v>
+        <v>1.155276478653089</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.8988188675235</v>
+        <v>14.57391729522987</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09774282277274977</v>
+        <v>0.09765875827684528</v>
       </c>
       <c r="C14">
-        <v>126.4183204591158</v>
+        <v>125.1995528414822</v>
       </c>
       <c r="D14">
-        <v>126.6063204591158</v>
+        <v>126.8115528414822</v>
       </c>
       <c r="E14">
-        <v>-24.21199999999999</v>
+        <v>-22.78799999999999</v>
       </c>
       <c r="F14">
-        <v>17.088</v>
+        <v>18.512</v>
       </c>
       <c r="G14">
         <v>16.9</v>
@@ -2563,28 +2563,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M14">
-        <v>0.8595263999999998</v>
+        <v>0.9311535999999998</v>
       </c>
       <c r="N14">
-        <v>11.66714026666667</v>
+        <v>11.59551306666667</v>
       </c>
       <c r="O14">
-        <v>1.458392533333333</v>
+        <v>1.449439133333333</v>
       </c>
       <c r="P14">
-        <v>10.20874773333333</v>
+        <v>10.14607393333333</v>
       </c>
       <c r="Q14">
-        <v>13.14874773333333</v>
+        <v>13.08607393333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1050696849690338</v>
+        <v>0.1056748658354544</v>
       </c>
       <c r="T14">
-        <v>1.155276478653089</v>
+        <v>1.167072580162179</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.57391729522987</v>
+        <v>13.45284673405834</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09765875827684528</v>
+        <v>0.09775844378094077</v>
       </c>
       <c r="C15">
-        <v>125.1995528414822</v>
+        <v>123.5322569948354</v>
       </c>
       <c r="D15">
-        <v>126.8115528414822</v>
+        <v>126.5682569948354</v>
       </c>
       <c r="E15">
-        <v>-22.78799999999999</v>
+        <v>-21.36399999999999</v>
       </c>
       <c r="F15">
-        <v>18.512</v>
+        <v>19.936</v>
       </c>
       <c r="G15">
         <v>16.9</v>
@@ -2645,45 +2645,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M15">
-        <v>0.9311535999999998</v>
+        <v>1.0326848</v>
       </c>
       <c r="N15">
-        <v>11.59551306666667</v>
+        <v>11.49398186666667</v>
       </c>
       <c r="O15">
-        <v>1.449439133333333</v>
+        <v>1.436747733333333</v>
       </c>
       <c r="P15">
-        <v>10.14607393333333</v>
+        <v>10.05723413333333</v>
       </c>
       <c r="Q15">
-        <v>13.08607393333333</v>
+        <v>12.99723413333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1056748658354544</v>
+        <v>0.1062941206755125</v>
       </c>
       <c r="T15">
-        <v>1.167072580162179</v>
+        <v>1.17914300961334</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.45284673405834</v>
+        <v>12.1301937112531</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09775844378094077</v>
+        <v>0.09768750428503627</v>
       </c>
       <c r="C16">
-        <v>123.5322569948354</v>
+        <v>122.2812984327007</v>
       </c>
       <c r="D16">
-        <v>126.5682569948354</v>
+        <v>126.7412984327007</v>
       </c>
       <c r="E16">
-        <v>-21.36399999999999</v>
+        <v>-19.93999999999999</v>
       </c>
       <c r="F16">
-        <v>19.936</v>
+        <v>21.36</v>
       </c>
       <c r="G16">
         <v>16.9</v>
@@ -2727,28 +2727,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M16">
-        <v>1.0326848</v>
+        <v>1.106448</v>
       </c>
       <c r="N16">
-        <v>11.49398186666667</v>
+        <v>11.42021866666667</v>
       </c>
       <c r="O16">
-        <v>1.436747733333333</v>
+        <v>1.427527333333333</v>
       </c>
       <c r="P16">
-        <v>10.05723413333333</v>
+        <v>9.992691333333333</v>
       </c>
       <c r="Q16">
-        <v>12.99723413333333</v>
+        <v>12.93269133333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1062941206755125</v>
+        <v>0.1069279462176897</v>
       </c>
       <c r="T16">
-        <v>1.17914300961334</v>
+        <v>1.191497449169235</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.1301937112531</v>
+        <v>11.3215141305029</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09768750428503625</v>
+        <v>0.09761656478913175</v>
       </c>
       <c r="C17">
-        <v>122.2812984327007</v>
+        <v>121.0308136755133</v>
       </c>
       <c r="D17">
-        <v>126.7412984327007</v>
+        <v>126.9148136755133</v>
       </c>
       <c r="E17">
-        <v>-19.93999999999999</v>
+        <v>-18.51599999999999</v>
       </c>
       <c r="F17">
-        <v>21.36</v>
+        <v>22.784</v>
       </c>
       <c r="G17">
         <v>16.9</v>
@@ -2809,28 +2809,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M17">
-        <v>1.106448</v>
+        <v>1.1802112</v>
       </c>
       <c r="N17">
-        <v>11.42021866666667</v>
+        <v>11.34645546666667</v>
       </c>
       <c r="O17">
-        <v>1.427527333333333</v>
+        <v>1.418306933333333</v>
       </c>
       <c r="P17">
-        <v>9.992691333333333</v>
+        <v>9.928148533333333</v>
       </c>
       <c r="Q17">
-        <v>12.93269133333333</v>
+        <v>12.86814853333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1069279462176897</v>
+        <v>0.1075768628442045</v>
       </c>
       <c r="T17">
-        <v>1.191497449169235</v>
+        <v>1.20414604204789</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.3215141305029</v>
+        <v>10.61391949734647</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09761656478913175</v>
+        <v>0.09754562529322724</v>
       </c>
       <c r="C18">
-        <v>121.0308136755133</v>
+        <v>119.7808046719296</v>
       </c>
       <c r="D18">
-        <v>126.9148136755133</v>
+        <v>127.0888046719296</v>
       </c>
       <c r="E18">
-        <v>-18.51599999999999</v>
+        <v>-17.09199999999999</v>
       </c>
       <c r="F18">
-        <v>22.784</v>
+        <v>24.208</v>
       </c>
       <c r="G18">
         <v>16.9</v>
@@ -2891,28 +2891,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M18">
-        <v>1.1802112</v>
+        <v>1.2539744</v>
       </c>
       <c r="N18">
-        <v>11.34645546666667</v>
+        <v>11.27269226666667</v>
       </c>
       <c r="O18">
-        <v>1.418306933333333</v>
+        <v>1.409086533333333</v>
       </c>
       <c r="P18">
-        <v>9.928148533333333</v>
+        <v>9.863605733333333</v>
       </c>
       <c r="Q18">
-        <v>12.86814853333333</v>
+        <v>12.80360573333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1075768628442045</v>
+        <v>0.1082414160159365</v>
       </c>
       <c r="T18">
-        <v>1.20414604204789</v>
+        <v>1.217099420297114</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.61391949734647</v>
+        <v>9.989571291620202</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09754562529322724</v>
+        <v>0.09774243579732275</v>
       </c>
       <c r="C19">
-        <v>119.7808046719296</v>
+        <v>117.8752636866363</v>
       </c>
       <c r="D19">
-        <v>127.0888046719296</v>
+        <v>126.6072636866363</v>
       </c>
       <c r="E19">
-        <v>-17.09199999999999</v>
+        <v>-15.66799999999999</v>
       </c>
       <c r="F19">
-        <v>24.208</v>
+        <v>25.632</v>
       </c>
       <c r="G19">
         <v>16.9</v>
@@ -2973,45 +2973,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M19">
-        <v>1.2539744</v>
+        <v>1.371312</v>
       </c>
       <c r="N19">
-        <v>11.27269226666667</v>
+        <v>11.15535466666667</v>
       </c>
       <c r="O19">
-        <v>1.409086533333333</v>
+        <v>1.394419333333333</v>
       </c>
       <c r="P19">
-        <v>9.863605733333333</v>
+        <v>9.760935333333334</v>
       </c>
       <c r="Q19">
-        <v>12.80360573333333</v>
+        <v>12.70093533333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1082414160159365</v>
+        <v>0.1089221778016131</v>
       </c>
       <c r="T19">
-        <v>1.217099420297114</v>
+        <v>1.230368734601197</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.989571291620202</v>
+        <v>9.134804236137851</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09774243579732277</v>
+        <v>0.09768637130141823</v>
       </c>
       <c r="C20">
-        <v>117.8752636866363</v>
+        <v>116.588065938141</v>
       </c>
       <c r="D20">
-        <v>126.6072636866363</v>
+        <v>126.744065938141</v>
       </c>
       <c r="E20">
-        <v>-15.668</v>
+        <v>-14.24399999999999</v>
       </c>
       <c r="F20">
-        <v>25.63199999999999</v>
+        <v>27.056</v>
       </c>
       <c r="G20">
         <v>16.9</v>
@@ -3055,28 +3055,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M20">
-        <v>1.371312</v>
+        <v>1.447496</v>
       </c>
       <c r="N20">
-        <v>11.15535466666667</v>
+        <v>11.07917066666667</v>
       </c>
       <c r="O20">
-        <v>1.394419333333333</v>
+        <v>1.384896333333334</v>
       </c>
       <c r="P20">
-        <v>9.760935333333334</v>
+        <v>9.694274333333334</v>
       </c>
       <c r="Q20">
-        <v>12.70093533333333</v>
+        <v>12.63427433333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1089221778016131</v>
+        <v>0.1096197485202694</v>
       </c>
       <c r="T20">
-        <v>1.230368734601197</v>
+        <v>1.243965686295505</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.134804236137853</v>
+        <v>8.654025065814807</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09768637130141823</v>
+        <v>0.09763030680551374</v>
       </c>
       <c r="C21">
-        <v>116.588065938141</v>
+        <v>115.3011641458049</v>
       </c>
       <c r="D21">
-        <v>126.744065938141</v>
+        <v>126.8811641458049</v>
       </c>
       <c r="E21">
-        <v>-14.24399999999999</v>
+        <v>-12.81999999999999</v>
       </c>
       <c r="F21">
-        <v>27.056</v>
+        <v>28.48</v>
       </c>
       <c r="G21">
         <v>16.9</v>
@@ -3137,28 +3137,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M21">
-        <v>1.447496</v>
+        <v>1.52368</v>
       </c>
       <c r="N21">
-        <v>11.07917066666667</v>
+        <v>11.00298666666667</v>
       </c>
       <c r="O21">
-        <v>1.384896333333334</v>
+        <v>1.375373333333334</v>
       </c>
       <c r="P21">
-        <v>9.694274333333334</v>
+        <v>9.627613333333334</v>
       </c>
       <c r="Q21">
-        <v>12.63427433333333</v>
+        <v>12.56761333333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1096197485202694</v>
+        <v>0.1103347585068922</v>
       </c>
       <c r="T21">
-        <v>1.243965686295505</v>
+        <v>1.25790256178217</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.654025065814807</v>
+        <v>8.221323812524068</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09763030680551374</v>
+        <v>0.09757424230960923</v>
       </c>
       <c r="C22">
-        <v>115.3011641458049</v>
+        <v>114.0145592710695</v>
       </c>
       <c r="D22">
-        <v>126.8811641458049</v>
+        <v>127.0185592710695</v>
       </c>
       <c r="E22">
-        <v>-12.81999999999999</v>
+        <v>-11.39599999999999</v>
       </c>
       <c r="F22">
-        <v>28.48</v>
+        <v>29.904</v>
       </c>
       <c r="G22">
         <v>16.9</v>
@@ -3219,28 +3219,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M22">
-        <v>1.52368</v>
+        <v>1.599864</v>
       </c>
       <c r="N22">
-        <v>11.00298666666667</v>
+        <v>10.92680266666667</v>
       </c>
       <c r="O22">
-        <v>1.375373333333334</v>
+        <v>1.365850333333333</v>
       </c>
       <c r="P22">
-        <v>9.627613333333334</v>
+        <v>9.560952333333333</v>
       </c>
       <c r="Q22">
-        <v>12.56761333333333</v>
+        <v>12.50095233333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1103347585068922</v>
+        <v>0.1110678700121636</v>
       </c>
       <c r="T22">
-        <v>1.25790256178217</v>
+        <v>1.272192269559637</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.221323812524068</v>
+        <v>7.829832202403872</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09757424230960923</v>
+        <v>0.09767217781370474</v>
       </c>
       <c r="C23">
-        <v>114.0145592710695</v>
+        <v>112.3507461929225</v>
       </c>
       <c r="D23">
-        <v>127.0185592710695</v>
+        <v>126.7787461929225</v>
       </c>
       <c r="E23">
-        <v>-11.396</v>
+        <v>-9.971999999999994</v>
       </c>
       <c r="F23">
-        <v>29.90399999999999</v>
+        <v>31.328</v>
       </c>
       <c r="G23">
         <v>16.9</v>
@@ -3301,45 +3301,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M23">
-        <v>1.599864</v>
+        <v>1.7011104</v>
       </c>
       <c r="N23">
-        <v>10.92680266666667</v>
+        <v>10.82555626666667</v>
       </c>
       <c r="O23">
-        <v>1.365850333333333</v>
+        <v>1.353194533333334</v>
       </c>
       <c r="P23">
-        <v>9.560952333333333</v>
+        <v>9.472361733333335</v>
       </c>
       <c r="Q23">
-        <v>12.50095233333333</v>
+        <v>12.41236173333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1110678700121636</v>
+        <v>0.1118197792483394</v>
       </c>
       <c r="T23">
-        <v>1.272192269559637</v>
+        <v>1.286848380100629</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.829832202403874</v>
+        <v>7.363817578604345</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09767217781370474</v>
+        <v>0.09762311331780023</v>
       </c>
       <c r="C24">
-        <v>112.3507461929225</v>
+        <v>111.0467763276467</v>
       </c>
       <c r="D24">
-        <v>126.7787461929225</v>
+        <v>126.8987763276467</v>
       </c>
       <c r="E24">
-        <v>-9.971999999999994</v>
+        <v>-8.547999999999995</v>
       </c>
       <c r="F24">
-        <v>31.328</v>
+        <v>32.752</v>
       </c>
       <c r="G24">
         <v>16.9</v>
@@ -3383,28 +3383,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M24">
-        <v>1.7011104</v>
+        <v>1.7784336</v>
       </c>
       <c r="N24">
-        <v>10.82555626666667</v>
+        <v>10.74823306666667</v>
       </c>
       <c r="O24">
-        <v>1.353194533333334</v>
+        <v>1.343529133333333</v>
       </c>
       <c r="P24">
-        <v>9.472361733333335</v>
+        <v>9.404703933333334</v>
       </c>
       <c r="Q24">
-        <v>12.41236173333333</v>
+        <v>12.34470393333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1118197792483394</v>
+        <v>0.1125912185945457</v>
       </c>
       <c r="T24">
-        <v>1.286848380100629</v>
+        <v>1.301885168837491</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.363817578604345</v>
+        <v>7.043651596925895</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09762311331780023</v>
+        <v>0.09757404882189573</v>
       </c>
       <c r="C25">
-        <v>111.0467763276467</v>
+        <v>109.7430339592805</v>
       </c>
       <c r="D25">
-        <v>126.8987763276467</v>
+        <v>127.0190339592804</v>
       </c>
       <c r="E25">
-        <v>-8.547999999999995</v>
+        <v>-7.123999999999995</v>
       </c>
       <c r="F25">
-        <v>32.752</v>
+        <v>34.17599999999999</v>
       </c>
       <c r="G25">
         <v>16.9</v>
@@ -3465,28 +3465,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M25">
-        <v>1.7784336</v>
+        <v>1.8557568</v>
       </c>
       <c r="N25">
-        <v>10.74823306666667</v>
+        <v>10.67090986666667</v>
       </c>
       <c r="O25">
-        <v>1.343529133333333</v>
+        <v>1.333863733333333</v>
       </c>
       <c r="P25">
-        <v>9.404703933333334</v>
+        <v>9.337046133333335</v>
       </c>
       <c r="Q25">
-        <v>12.34470393333333</v>
+        <v>12.27704613333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1125912185945457</v>
+        <v>0.1133829589761786</v>
       </c>
       <c r="T25">
-        <v>1.301885168837491</v>
+        <v>1.317317662541112</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.043651596925895</v>
+        <v>6.75016611372065</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0975740488218957</v>
+        <v>0.09752498432599123</v>
       </c>
       <c r="C26">
-        <v>109.7430339592806</v>
+        <v>108.4395197352106</v>
       </c>
       <c r="D26">
-        <v>127.0190339592805</v>
+        <v>127.1395197352106</v>
       </c>
       <c r="E26">
-        <v>-7.123999999999995</v>
+        <v>-5.699999999999996</v>
       </c>
       <c r="F26">
-        <v>34.17599999999999</v>
+        <v>35.59999999999999</v>
       </c>
       <c r="G26">
         <v>16.9</v>
@@ -3547,28 +3547,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M26">
-        <v>1.8557568</v>
+        <v>1.93308</v>
       </c>
       <c r="N26">
-        <v>10.67090986666667</v>
+        <v>10.59358666666667</v>
       </c>
       <c r="O26">
-        <v>1.333863733333333</v>
+        <v>1.324198333333333</v>
       </c>
       <c r="P26">
-        <v>9.337046133333335</v>
+        <v>9.269388333333334</v>
       </c>
       <c r="Q26">
-        <v>12.27704613333333</v>
+        <v>12.20938833333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1133829589761786</v>
+        <v>0.114195812434655</v>
       </c>
       <c r="T26">
-        <v>1.317317662541112</v>
+        <v>1.333161689410163</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.75016611372065</v>
+        <v>6.480159469171824</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09752498432599123</v>
+        <v>0.09747591983008669</v>
       </c>
       <c r="C27">
-        <v>108.4395197352106</v>
+        <v>107.1362343052823</v>
       </c>
       <c r="D27">
-        <v>127.1395197352106</v>
+        <v>127.2602343052823</v>
       </c>
       <c r="E27">
-        <v>-5.699999999999996</v>
+        <v>-4.275999999999996</v>
       </c>
       <c r="F27">
-        <v>35.59999999999999</v>
+        <v>37.02399999999999</v>
       </c>
       <c r="G27">
         <v>16.9</v>
@@ -3629,28 +3629,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M27">
-        <v>1.93308</v>
+        <v>2.0104032</v>
       </c>
       <c r="N27">
-        <v>10.59358666666667</v>
+        <v>10.51626346666667</v>
       </c>
       <c r="O27">
-        <v>1.324198333333333</v>
+        <v>1.314532933333334</v>
       </c>
       <c r="P27">
-        <v>9.269388333333334</v>
+        <v>9.201730533333334</v>
       </c>
       <c r="Q27">
-        <v>12.20938833333333</v>
+        <v>12.14173053333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.114195812434655</v>
+        <v>0.1150306349055226</v>
       </c>
       <c r="T27">
-        <v>1.333161689410163</v>
+        <v>1.349433933221621</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.480159469171824</v>
+        <v>6.230922566511369</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09747591983008669</v>
+        <v>0.0976631053341822</v>
       </c>
       <c r="C28">
-        <v>107.1362343052823</v>
+        <v>105.2529237615682</v>
       </c>
       <c r="D28">
-        <v>127.2602343052823</v>
+        <v>126.8009237615682</v>
       </c>
       <c r="E28">
-        <v>-4.275999999999996</v>
+        <v>-2.851999999999997</v>
       </c>
       <c r="F28">
-        <v>37.02399999999999</v>
+        <v>38.44799999999999</v>
       </c>
       <c r="G28">
         <v>16.9</v>
@@ -3711,45 +3711,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M28">
-        <v>2.0104032</v>
+        <v>2.1261744</v>
       </c>
       <c r="N28">
-        <v>10.51626346666667</v>
+        <v>10.40049226666667</v>
       </c>
       <c r="O28">
-        <v>1.314532933333334</v>
+        <v>1.300061533333333</v>
       </c>
       <c r="P28">
-        <v>9.201730533333334</v>
+        <v>9.100430733333333</v>
       </c>
       <c r="Q28">
-        <v>12.14173053333333</v>
+        <v>12.04043073333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1150306349055226</v>
+        <v>0.1158883292249071</v>
       </c>
       <c r="T28">
-        <v>1.349433933221621</v>
+        <v>1.366151991932024</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.230922566511369</v>
+        <v>5.89164589069771</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0976631053341822</v>
+        <v>0.09762279083827771</v>
       </c>
       <c r="C29">
-        <v>105.2529237615682</v>
+        <v>103.9275659851725</v>
       </c>
       <c r="D29">
-        <v>126.8009237615682</v>
+        <v>126.8995659851725</v>
       </c>
       <c r="E29">
-        <v>-2.851999999999997</v>
+        <v>-1.42799999999999</v>
       </c>
       <c r="F29">
-        <v>38.44799999999999</v>
+        <v>39.872</v>
       </c>
       <c r="G29">
         <v>16.9</v>
@@ -3793,28 +3793,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M29">
-        <v>2.1261744</v>
+        <v>2.2049216</v>
       </c>
       <c r="N29">
-        <v>10.40049226666667</v>
+        <v>10.32174506666667</v>
       </c>
       <c r="O29">
-        <v>1.300061533333333</v>
+        <v>1.290218133333333</v>
       </c>
       <c r="P29">
-        <v>9.100430733333333</v>
+        <v>9.031526933333334</v>
       </c>
       <c r="Q29">
-        <v>12.04043073333333</v>
+        <v>11.97152693333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1158883292249071</v>
+        <v>0.1167698483864968</v>
       </c>
       <c r="T29">
-        <v>1.366151991932024</v>
+        <v>1.383334441162159</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.89164589069771</v>
+        <v>5.681229966029933</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09762279083827771</v>
+        <v>0.0975824763423732</v>
       </c>
       <c r="C30">
-        <v>103.9275659851725</v>
+        <v>102.6023618017219</v>
       </c>
       <c r="D30">
-        <v>126.8995659851725</v>
+        <v>126.9983618017219</v>
       </c>
       <c r="E30">
-        <v>-1.42799999999999</v>
+        <v>-0.003999999999990678</v>
       </c>
       <c r="F30">
-        <v>39.872</v>
+        <v>41.296</v>
       </c>
       <c r="G30">
         <v>16.9</v>
@@ -3875,28 +3875,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M30">
-        <v>2.2049216</v>
+        <v>2.2836688</v>
       </c>
       <c r="N30">
-        <v>10.32174506666667</v>
+        <v>10.24299786666667</v>
       </c>
       <c r="O30">
-        <v>1.290218133333333</v>
+        <v>1.280374733333333</v>
       </c>
       <c r="P30">
-        <v>9.031526933333334</v>
+        <v>8.962623133333333</v>
       </c>
       <c r="Q30">
-        <v>11.97152693333333</v>
+        <v>11.90262313333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1167698483864968</v>
+        <v>0.1176761990737651</v>
       </c>
       <c r="T30">
-        <v>1.383334441162159</v>
+        <v>1.401000903046665</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.681229966029933</v>
+        <v>5.485325484442694</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09758247634237319</v>
+        <v>0.09754216184646869</v>
       </c>
       <c r="C31">
-        <v>102.602361801722</v>
+        <v>101.2773115702284</v>
       </c>
       <c r="D31">
-        <v>126.998361801722</v>
+        <v>127.0973115702285</v>
       </c>
       <c r="E31">
-        <v>-0.003999999999997783</v>
+        <v>1.420000000000002</v>
       </c>
       <c r="F31">
-        <v>41.29599999999999</v>
+        <v>42.71999999999999</v>
       </c>
       <c r="G31">
         <v>16.9</v>
@@ -3957,28 +3957,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M31">
-        <v>2.2836688</v>
+        <v>2.362416</v>
       </c>
       <c r="N31">
-        <v>10.24299786666667</v>
+        <v>10.16425066666667</v>
       </c>
       <c r="O31">
-        <v>1.280374733333334</v>
+        <v>1.270531333333333</v>
       </c>
       <c r="P31">
-        <v>8.962623133333334</v>
+        <v>8.893719333333333</v>
       </c>
       <c r="Q31">
-        <v>11.90262313333333</v>
+        <v>11.83371933333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1176761990737651</v>
+        <v>0.1186084454949553</v>
       </c>
       <c r="T31">
-        <v>1.401000903046664</v>
+        <v>1.419172120985013</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.485325484442696</v>
+        <v>5.302481301627939</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09754216184646869</v>
+        <v>0.09750184735056419</v>
       </c>
       <c r="C32">
-        <v>101.2773115702284</v>
+        <v>99.95241565082402</v>
       </c>
       <c r="D32">
-        <v>127.0973115702285</v>
+        <v>127.196415650824</v>
       </c>
       <c r="E32">
-        <v>1.420000000000002</v>
+        <v>2.844000000000001</v>
       </c>
       <c r="F32">
-        <v>42.71999999999999</v>
+        <v>44.14399999999999</v>
       </c>
       <c r="G32">
         <v>16.9</v>
@@ -4039,28 +4039,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M32">
-        <v>2.362416</v>
+        <v>2.4411632</v>
       </c>
       <c r="N32">
-        <v>10.16425066666667</v>
+        <v>10.08550346666667</v>
       </c>
       <c r="O32">
-        <v>1.270531333333333</v>
+        <v>1.260687933333333</v>
       </c>
       <c r="P32">
-        <v>8.893719333333333</v>
+        <v>8.824815533333334</v>
       </c>
       <c r="Q32">
-        <v>11.83371933333333</v>
+        <v>11.76481553333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1186084454949553</v>
+        <v>0.1195677135515423</v>
       </c>
       <c r="T32">
-        <v>1.419172120985013</v>
+        <v>1.437870040892589</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.302481301627939</v>
+        <v>5.131433517704457</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09750184735056419</v>
+        <v>0.09746153285465967</v>
       </c>
       <c r="C33">
-        <v>99.95241565082402</v>
+        <v>98.62767440476483</v>
       </c>
       <c r="D33">
-        <v>127.196415650824</v>
+        <v>127.2956744047648</v>
       </c>
       <c r="E33">
-        <v>2.844000000000001</v>
+        <v>4.268000000000001</v>
       </c>
       <c r="F33">
-        <v>44.14399999999999</v>
+        <v>45.56799999999999</v>
       </c>
       <c r="G33">
         <v>16.9</v>
@@ -4121,28 +4121,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M33">
-        <v>2.4411632</v>
+        <v>2.5199104</v>
       </c>
       <c r="N33">
-        <v>10.08550346666667</v>
+        <v>10.00675626666667</v>
       </c>
       <c r="O33">
-        <v>1.260687933333333</v>
+        <v>1.250844533333333</v>
       </c>
       <c r="P33">
-        <v>8.824815533333334</v>
+        <v>8.755911733333333</v>
       </c>
       <c r="Q33">
-        <v>11.76481553333333</v>
+        <v>11.69591173333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1195677135515423</v>
+        <v>0.1205551953744995</v>
       </c>
       <c r="T33">
-        <v>1.437870040892589</v>
+        <v>1.457117899620976</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.131433517704457</v>
+        <v>4.971076220276192</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09746153285465967</v>
+        <v>0.09742121835875517</v>
       </c>
       <c r="C34">
-        <v>98.62767440476483</v>
+        <v>97.3030881944353</v>
       </c>
       <c r="D34">
-        <v>127.2956744047648</v>
+        <v>127.3950881944353</v>
       </c>
       <c r="E34">
-        <v>4.268000000000001</v>
+        <v>5.692000000000007</v>
       </c>
       <c r="F34">
-        <v>45.56799999999999</v>
+        <v>46.992</v>
       </c>
       <c r="G34">
         <v>16.9</v>
@@ -4203,28 +4203,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M34">
-        <v>2.5199104</v>
+        <v>2.5986576</v>
       </c>
       <c r="N34">
-        <v>10.00675626666667</v>
+        <v>9.928009066666668</v>
       </c>
       <c r="O34">
-        <v>1.250844533333333</v>
+        <v>1.241001133333334</v>
       </c>
       <c r="P34">
-        <v>8.755911733333333</v>
+        <v>8.687007933333334</v>
       </c>
       <c r="Q34">
-        <v>11.69591173333333</v>
+        <v>11.62700793333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1205551953744995</v>
+        <v>0.1215721542667988</v>
       </c>
       <c r="T34">
-        <v>1.457117899620976</v>
+        <v>1.476940321296479</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.971076220276192</v>
+        <v>4.820437546934489</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09742121835875517</v>
+        <v>0.09738090386285066</v>
       </c>
       <c r="C35">
-        <v>97.3030881944353</v>
+        <v>95.97865738335307</v>
       </c>
       <c r="D35">
-        <v>127.3950881944353</v>
+        <v>127.4946573833531</v>
       </c>
       <c r="E35">
-        <v>5.692000000000007</v>
+        <v>7.116000000000007</v>
       </c>
       <c r="F35">
-        <v>46.992</v>
+        <v>48.416</v>
       </c>
       <c r="G35">
         <v>16.9</v>
@@ -4285,28 +4285,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M35">
-        <v>2.5986576</v>
+        <v>2.6774048</v>
       </c>
       <c r="N35">
-        <v>9.928009066666668</v>
+        <v>9.849261866666668</v>
       </c>
       <c r="O35">
-        <v>1.241001133333334</v>
+        <v>1.231157733333333</v>
       </c>
       <c r="P35">
-        <v>8.687007933333334</v>
+        <v>8.618104133333334</v>
       </c>
       <c r="Q35">
-        <v>11.62700793333333</v>
+        <v>11.55810413333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1215721542667988</v>
+        <v>0.1226199300952283</v>
       </c>
       <c r="T35">
-        <v>1.476940321296479</v>
+        <v>1.497363422416694</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.820437546934489</v>
+        <v>4.678659972024652</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09738090386285066</v>
+        <v>0.09734058936694615</v>
       </c>
       <c r="C36">
-        <v>95.97865738335307</v>
+        <v>94.65438233617297</v>
       </c>
       <c r="D36">
-        <v>127.4946573833531</v>
+        <v>127.594382336173</v>
       </c>
       <c r="E36">
-        <v>7.116000000000007</v>
+        <v>8.540000000000006</v>
       </c>
       <c r="F36">
-        <v>48.416</v>
+        <v>49.84</v>
       </c>
       <c r="G36">
         <v>16.9</v>
@@ -4367,28 +4367,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M36">
-        <v>2.6774048</v>
+        <v>2.756152</v>
       </c>
       <c r="N36">
-        <v>9.849261866666668</v>
+        <v>9.770514666666667</v>
       </c>
       <c r="O36">
-        <v>1.231157733333333</v>
+        <v>1.221314333333333</v>
       </c>
       <c r="P36">
-        <v>8.618104133333334</v>
+        <v>8.549200333333333</v>
       </c>
       <c r="Q36">
-        <v>11.55810413333333</v>
+        <v>11.48920033333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1226199300952283</v>
+        <v>0.1236999451799172</v>
       </c>
       <c r="T36">
-        <v>1.497363422416694</v>
+        <v>1.5184149266483</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.678659972024652</v>
+        <v>4.544983972823948</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09734058936694615</v>
+        <v>0.09808777487104164</v>
       </c>
       <c r="C37">
-        <v>94.65438233617297</v>
+        <v>91.40707520327742</v>
       </c>
       <c r="D37">
-        <v>127.594382336173</v>
+        <v>125.7710752032774</v>
       </c>
       <c r="E37">
-        <v>8.540000000000006</v>
+        <v>9.964000000000006</v>
       </c>
       <c r="F37">
-        <v>49.84</v>
+        <v>51.264</v>
       </c>
       <c r="G37">
         <v>16.9</v>
@@ -4449,45 +4449,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M37">
-        <v>2.756152</v>
+        <v>2.9630592</v>
       </c>
       <c r="N37">
-        <v>9.770514666666667</v>
+        <v>9.563607466666667</v>
       </c>
       <c r="O37">
-        <v>1.221314333333333</v>
+        <v>1.195450933333333</v>
       </c>
       <c r="P37">
-        <v>8.549200333333333</v>
+        <v>8.368156533333334</v>
       </c>
       <c r="Q37">
-        <v>11.48920033333333</v>
+        <v>11.30815653333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1236999451799172</v>
+        <v>0.1248137107360026</v>
       </c>
       <c r="T37">
-        <v>1.5184149266483</v>
+        <v>1.540124290387145</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.544983972823948</v>
+        <v>4.227612687139922</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09808777487104166</v>
+        <v>0.09806933537513715</v>
       </c>
       <c r="C38">
-        <v>91.4070752032774</v>
+        <v>90.02744453013932</v>
       </c>
       <c r="D38">
-        <v>125.7710752032774</v>
+        <v>125.8154445301393</v>
       </c>
       <c r="E38">
-        <v>9.963999999999999</v>
+        <v>11.388</v>
       </c>
       <c r="F38">
-        <v>51.26399999999999</v>
+        <v>52.68799999999999</v>
       </c>
       <c r="G38">
         <v>16.9</v>
@@ -4531,28 +4531,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M38">
-        <v>2.9630592</v>
+        <v>3.045366399999999</v>
       </c>
       <c r="N38">
-        <v>9.563607466666667</v>
+        <v>9.481300266666668</v>
       </c>
       <c r="O38">
-        <v>1.195450933333333</v>
+        <v>1.185162533333334</v>
       </c>
       <c r="P38">
-        <v>8.368156533333334</v>
+        <v>8.296137733333335</v>
       </c>
       <c r="Q38">
-        <v>11.30815653333333</v>
+        <v>11.23613773333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1248137107360026</v>
+        <v>0.1259628339287891</v>
       </c>
       <c r="T38">
-        <v>1.540124290387145</v>
+        <v>1.562522840276428</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.227612687139922</v>
+        <v>4.11335288478479</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09806933537513715</v>
+        <v>0.09805089587923264</v>
       </c>
       <c r="C39">
-        <v>90.02744453013932</v>
+        <v>88.64784517313498</v>
       </c>
       <c r="D39">
-        <v>125.8154445301393</v>
+        <v>125.859845173135</v>
       </c>
       <c r="E39">
-        <v>11.388</v>
+        <v>12.812</v>
       </c>
       <c r="F39">
-        <v>52.68799999999999</v>
+        <v>54.11199999999999</v>
       </c>
       <c r="G39">
         <v>16.9</v>
@@ -4613,28 +4613,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M39">
-        <v>3.045366399999999</v>
+        <v>3.1276736</v>
       </c>
       <c r="N39">
-        <v>9.481300266666668</v>
+        <v>9.398993066666668</v>
       </c>
       <c r="O39">
-        <v>1.185162533333334</v>
+        <v>1.174874133333333</v>
       </c>
       <c r="P39">
-        <v>8.296137733333335</v>
+        <v>8.224118933333335</v>
       </c>
       <c r="Q39">
-        <v>11.23613773333333</v>
+        <v>11.16411893333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1259628339287891</v>
+        <v>0.1271490256116656</v>
       </c>
       <c r="T39">
-        <v>1.562522840276428</v>
+        <v>1.585643924033108</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.11335288478479</v>
+        <v>4.00510675623782</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09805089587923264</v>
+        <v>0.09922683138332813</v>
       </c>
       <c r="C40">
-        <v>88.64784517313498</v>
+        <v>84.45364419645429</v>
       </c>
       <c r="D40">
-        <v>125.859845173135</v>
+        <v>123.0896441964543</v>
       </c>
       <c r="E40">
-        <v>12.812</v>
+        <v>14.236</v>
       </c>
       <c r="F40">
-        <v>54.11199999999999</v>
+        <v>55.53599999999999</v>
       </c>
       <c r="G40">
         <v>16.9</v>
@@ -4695,45 +4695,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M40">
-        <v>3.1276736</v>
+        <v>3.4043568</v>
       </c>
       <c r="N40">
-        <v>9.398993066666668</v>
+        <v>9.122309866666669</v>
       </c>
       <c r="O40">
-        <v>1.174874133333333</v>
+        <v>1.140288733333334</v>
       </c>
       <c r="P40">
-        <v>8.224118933333335</v>
+        <v>7.982021133333335</v>
       </c>
       <c r="Q40">
-        <v>11.16411893333333</v>
+        <v>10.92202113333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1271490256116656</v>
+        <v>0.1283741088251281</v>
       </c>
       <c r="T40">
-        <v>1.585643924033108</v>
+        <v>1.609523076109679</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.00510675623782</v>
+        <v>3.679598644497742</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09922683138332813</v>
+        <v>0.09923901688742365</v>
       </c>
       <c r="C41">
-        <v>84.45364419645429</v>
+        <v>83.00157651387265</v>
       </c>
       <c r="D41">
-        <v>123.0896441964543</v>
+        <v>123.0615765138727</v>
       </c>
       <c r="E41">
-        <v>14.236</v>
+        <v>15.66</v>
       </c>
       <c r="F41">
-        <v>55.53599999999999</v>
+        <v>56.95999999999999</v>
       </c>
       <c r="G41">
         <v>16.9</v>
@@ -4777,28 +4777,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M41">
-        <v>3.4043568</v>
+        <v>3.491648</v>
       </c>
       <c r="N41">
-        <v>9.122309866666669</v>
+        <v>9.035018666666668</v>
       </c>
       <c r="O41">
-        <v>1.140288733333334</v>
+        <v>1.129377333333333</v>
       </c>
       <c r="P41">
-        <v>7.982021133333335</v>
+        <v>7.905641333333334</v>
       </c>
       <c r="Q41">
-        <v>10.92202113333333</v>
+        <v>10.84564133333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1283741088251281</v>
+        <v>0.1296400281457061</v>
       </c>
       <c r="T41">
-        <v>1.609523076109679</v>
+        <v>1.634198199922136</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.679598644497742</v>
+        <v>3.587608678385298</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09923901688742365</v>
+        <v>0.09925120239151913</v>
       </c>
       <c r="C42">
-        <v>83.00157651387265</v>
+        <v>81.5495216287155</v>
       </c>
       <c r="D42">
-        <v>123.0615765138727</v>
+        <v>123.0335216287155</v>
       </c>
       <c r="E42">
-        <v>15.66</v>
+        <v>17.084</v>
       </c>
       <c r="F42">
-        <v>56.95999999999999</v>
+        <v>58.38399999999999</v>
       </c>
       <c r="G42">
         <v>16.9</v>
@@ -4859,28 +4859,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M42">
-        <v>3.491648</v>
+        <v>3.5789392</v>
       </c>
       <c r="N42">
-        <v>9.035018666666668</v>
+        <v>8.947727466666667</v>
       </c>
       <c r="O42">
-        <v>1.129377333333333</v>
+        <v>1.118465933333333</v>
       </c>
       <c r="P42">
-        <v>7.905641333333334</v>
+        <v>7.829261533333334</v>
       </c>
       <c r="Q42">
-        <v>10.84564133333333</v>
+        <v>10.76926153333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1296400281457061</v>
+        <v>0.1309488599856257</v>
       </c>
       <c r="T42">
-        <v>1.634198199922136</v>
+        <v>1.659709768609591</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.587608678385298</v>
+        <v>3.500106027692973</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09925120239151913</v>
+        <v>0.1002923878956146</v>
       </c>
       <c r="C43">
-        <v>81.5495216287155</v>
+        <v>77.77472137597141</v>
       </c>
       <c r="D43">
-        <v>123.0335216287155</v>
+        <v>120.6827213759714</v>
       </c>
       <c r="E43">
-        <v>17.084</v>
+        <v>18.508</v>
       </c>
       <c r="F43">
-        <v>58.38399999999999</v>
+        <v>59.80799999999999</v>
       </c>
       <c r="G43">
         <v>16.9</v>
@@ -4941,45 +4941,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M43">
-        <v>3.5789392</v>
+        <v>3.8336928</v>
       </c>
       <c r="N43">
-        <v>8.947727466666667</v>
+        <v>8.692973866666668</v>
       </c>
       <c r="O43">
-        <v>1.118465933333333</v>
+        <v>1.086621733333333</v>
       </c>
       <c r="P43">
-        <v>7.829261533333334</v>
+        <v>7.606352133333334</v>
       </c>
       <c r="Q43">
-        <v>10.76926153333333</v>
+        <v>10.54635213333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1309488599856257</v>
+        <v>0.1323028239579563</v>
       </c>
       <c r="T43">
-        <v>1.659709768609591</v>
+        <v>1.686101046562131</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.500106027692973</v>
+        <v>3.26751967885029</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1002923878956146</v>
+        <v>0.1003290733997101</v>
       </c>
       <c r="C44">
-        <v>77.77472137597141</v>
+        <v>76.26952970713739</v>
       </c>
       <c r="D44">
-        <v>120.6827213759714</v>
+        <v>120.6015297071374</v>
       </c>
       <c r="E44">
-        <v>18.508</v>
+        <v>19.932</v>
       </c>
       <c r="F44">
-        <v>59.80799999999999</v>
+        <v>61.23199999999999</v>
       </c>
       <c r="G44">
         <v>16.9</v>
@@ -5023,28 +5023,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M44">
-        <v>3.833692799999999</v>
+        <v>3.9249712</v>
       </c>
       <c r="N44">
-        <v>8.692973866666668</v>
+        <v>8.601695466666667</v>
       </c>
       <c r="O44">
-        <v>1.086621733333333</v>
+        <v>1.075211933333333</v>
       </c>
       <c r="P44">
-        <v>7.606352133333334</v>
+        <v>7.526483533333334</v>
       </c>
       <c r="Q44">
-        <v>10.54635213333333</v>
+        <v>10.46648353333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1323028239579563</v>
+        <v>0.1337042954380879</v>
       </c>
       <c r="T44">
-        <v>1.686101046562131</v>
+        <v>1.713418334267392</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.26751967885029</v>
+        <v>3.191530849109585</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1003290733997101</v>
+        <v>0.1003657589038056</v>
       </c>
       <c r="C45">
-        <v>76.26952970713739</v>
+        <v>74.76444721143174</v>
       </c>
       <c r="D45">
-        <v>120.6015297071374</v>
+        <v>120.5204472114317</v>
       </c>
       <c r="E45">
-        <v>19.932</v>
+        <v>21.356</v>
       </c>
       <c r="F45">
-        <v>61.23199999999999</v>
+        <v>62.65599999999999</v>
       </c>
       <c r="G45">
         <v>16.9</v>
@@ -5105,28 +5105,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M45">
-        <v>3.9249712</v>
+        <v>4.0162496</v>
       </c>
       <c r="N45">
-        <v>8.601695466666667</v>
+        <v>8.510417066666667</v>
       </c>
       <c r="O45">
-        <v>1.075211933333333</v>
+        <v>1.063802133333333</v>
       </c>
       <c r="P45">
-        <v>7.526483533333334</v>
+        <v>7.446614933333334</v>
       </c>
       <c r="Q45">
-        <v>10.46648353333333</v>
+        <v>10.38661493333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1337042954380879</v>
+        <v>0.1351558194710815</v>
       </c>
       <c r="T45">
-        <v>1.713418334267392</v>
+        <v>1.741711239390697</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.191530849109585</v>
+        <v>3.118996057084367</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1003657589038056</v>
+        <v>0.1004024444079011</v>
       </c>
       <c r="C46">
-        <v>74.76444721143174</v>
+        <v>73.25947366880543</v>
       </c>
       <c r="D46">
-        <v>120.5204472114317</v>
+        <v>120.4394736688054</v>
       </c>
       <c r="E46">
-        <v>21.356</v>
+        <v>22.78000000000001</v>
       </c>
       <c r="F46">
-        <v>62.65599999999999</v>
+        <v>64.08</v>
       </c>
       <c r="G46">
         <v>16.9</v>
@@ -5187,28 +5187,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M46">
-        <v>4.0162496</v>
+        <v>4.107528</v>
       </c>
       <c r="N46">
-        <v>8.510417066666667</v>
+        <v>8.419138666666667</v>
       </c>
       <c r="O46">
-        <v>1.063802133333333</v>
+        <v>1.052392333333333</v>
       </c>
       <c r="P46">
-        <v>7.446614933333334</v>
+        <v>7.366746333333333</v>
       </c>
       <c r="Q46">
-        <v>10.38661493333333</v>
+        <v>10.30674633333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1351558194710815</v>
+        <v>0.1366601261961838</v>
       </c>
       <c r="T46">
-        <v>1.741711239390697</v>
+        <v>1.771032977427578</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.118996057084367</v>
+        <v>3.049685033593603</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1004024444079011</v>
+        <v>0.1035786299119966</v>
       </c>
       <c r="C47">
-        <v>73.25947366880543</v>
+        <v>65.21471940428927</v>
       </c>
       <c r="D47">
-        <v>120.4394736688054</v>
+        <v>113.8187194042893</v>
       </c>
       <c r="E47">
-        <v>22.78000000000001</v>
+        <v>24.204</v>
       </c>
       <c r="F47">
-        <v>64.08</v>
+        <v>65.50399999999999</v>
       </c>
       <c r="G47">
         <v>16.9</v>
@@ -5269,45 +5269,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M47">
-        <v>4.107528</v>
+        <v>4.7097376</v>
       </c>
       <c r="N47">
-        <v>8.419138666666667</v>
+        <v>7.816929066666668</v>
       </c>
       <c r="O47">
-        <v>1.052392333333333</v>
+        <v>0.9771161333333335</v>
       </c>
       <c r="P47">
-        <v>7.366746333333333</v>
+        <v>6.839812933333334</v>
       </c>
       <c r="Q47">
-        <v>10.30674633333333</v>
+        <v>9.779812933333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1366601261961838</v>
+        <v>0.1382201479851789</v>
       </c>
       <c r="T47">
-        <v>1.771032977427578</v>
+        <v>1.80144070576212</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.049685033593603</v>
+        <v>2.659737703150738</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1035786299119966</v>
+        <v>0.1036835654160921</v>
       </c>
       <c r="C48">
-        <v>65.21471940428927</v>
+        <v>63.58438061692647</v>
       </c>
       <c r="D48">
-        <v>113.8187194042893</v>
+        <v>113.6123806169265</v>
       </c>
       <c r="E48">
-        <v>24.204</v>
+        <v>25.62800000000001</v>
       </c>
       <c r="F48">
-        <v>65.50399999999999</v>
+        <v>66.928</v>
       </c>
       <c r="G48">
         <v>16.9</v>
@@ -5351,28 +5351,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M48">
-        <v>4.7097376</v>
+        <v>4.8121232</v>
       </c>
       <c r="N48">
-        <v>7.816929066666668</v>
+        <v>7.714543466666667</v>
       </c>
       <c r="O48">
-        <v>0.9771161333333335</v>
+        <v>0.9643179333333334</v>
       </c>
       <c r="P48">
-        <v>6.839812933333334</v>
+        <v>6.750225533333333</v>
       </c>
       <c r="Q48">
-        <v>9.779812933333334</v>
+        <v>9.690225533333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1382201479851789</v>
+        <v>0.1398390385209285</v>
       </c>
       <c r="T48">
-        <v>1.80144070576212</v>
+        <v>1.83299589554325</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.659737703150738</v>
+        <v>2.603147539253913</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1036835654160921</v>
+        <v>0.1037885009201876</v>
       </c>
       <c r="C49">
-        <v>63.58438061692647</v>
+        <v>61.95478860743587</v>
       </c>
       <c r="D49">
-        <v>113.6123806169265</v>
+        <v>113.4067886074359</v>
       </c>
       <c r="E49">
-        <v>25.62800000000001</v>
+        <v>27.052</v>
       </c>
       <c r="F49">
-        <v>66.928</v>
+        <v>68.35199999999999</v>
       </c>
       <c r="G49">
         <v>16.9</v>
@@ -5433,28 +5433,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M49">
-        <v>4.8121232</v>
+        <v>4.914508799999999</v>
       </c>
       <c r="N49">
-        <v>7.714543466666667</v>
+        <v>7.612157866666668</v>
       </c>
       <c r="O49">
-        <v>0.9643179333333334</v>
+        <v>0.9515197333333335</v>
       </c>
       <c r="P49">
-        <v>6.750225533333333</v>
+        <v>6.660638133333334</v>
       </c>
       <c r="Q49">
-        <v>9.690225533333333</v>
+        <v>9.600638133333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1398390385209285</v>
+        <v>0.1415201940772839</v>
       </c>
       <c r="T49">
-        <v>1.83299589554325</v>
+        <v>1.865764746469807</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.603147539253913</v>
+        <v>2.548915298852791</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1037885009201876</v>
+        <v>0.1055655614242831</v>
       </c>
       <c r="C50">
-        <v>61.9547886074359</v>
+        <v>57.15876766213117</v>
       </c>
       <c r="D50">
-        <v>113.4067886074359</v>
+        <v>110.0347676621312</v>
       </c>
       <c r="E50">
-        <v>27.052</v>
+        <v>28.47599999999999</v>
       </c>
       <c r="F50">
-        <v>68.35199999999999</v>
+        <v>69.77599999999998</v>
       </c>
       <c r="G50">
         <v>16.9</v>
@@ -5515,45 +5515,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M50">
-        <v>4.914508799999999</v>
+        <v>5.289020799999999</v>
       </c>
       <c r="N50">
-        <v>7.612157866666668</v>
+        <v>7.237645866666668</v>
       </c>
       <c r="O50">
-        <v>0.9515197333333335</v>
+        <v>0.9047057333333335</v>
       </c>
       <c r="P50">
-        <v>6.660638133333334</v>
+        <v>6.332940133333334</v>
       </c>
       <c r="Q50">
-        <v>9.600638133333334</v>
+        <v>9.272940133333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1415201940772838</v>
+        <v>0.1432672773025159</v>
       </c>
       <c r="T50">
-        <v>1.865764746469807</v>
+        <v>1.899818650373876</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.548915298852791</v>
+        <v>2.368428323569208</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1055655614242831</v>
+        <v>0.1057046219283786</v>
       </c>
       <c r="C51">
-        <v>57.15876766213117</v>
+        <v>55.47933678273387</v>
       </c>
       <c r="D51">
-        <v>110.0347676621312</v>
+        <v>109.7793367827338</v>
       </c>
       <c r="E51">
-        <v>28.47599999999999</v>
+        <v>29.9</v>
       </c>
       <c r="F51">
-        <v>69.77599999999998</v>
+        <v>71.19999999999999</v>
       </c>
       <c r="G51">
         <v>16.9</v>
@@ -5597,28 +5597,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M51">
-        <v>5.289020799999999</v>
+        <v>5.39696</v>
       </c>
       <c r="N51">
-        <v>7.237645866666668</v>
+        <v>7.129706666666667</v>
       </c>
       <c r="O51">
-        <v>0.9047057333333335</v>
+        <v>0.8912133333333334</v>
       </c>
       <c r="P51">
-        <v>6.332940133333334</v>
+        <v>6.238493333333334</v>
       </c>
       <c r="Q51">
-        <v>9.272940133333334</v>
+        <v>9.178493333333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1432672773025159</v>
+        <v>0.1450842438567572</v>
       </c>
       <c r="T51">
-        <v>1.899818650373876</v>
+        <v>1.935234710434108</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.368428323569208</v>
+        <v>2.321059757097823</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1057046219283786</v>
+        <v>0.1058436824324741</v>
       </c>
       <c r="C52">
-        <v>55.47933678273387</v>
+        <v>53.80108905351696</v>
       </c>
       <c r="D52">
-        <v>109.7793367827338</v>
+        <v>109.525089053517</v>
       </c>
       <c r="E52">
-        <v>29.9</v>
+        <v>31.32400000000001</v>
       </c>
       <c r="F52">
-        <v>71.19999999999999</v>
+        <v>72.624</v>
       </c>
       <c r="G52">
         <v>16.9</v>
@@ -5679,28 +5679,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M52">
-        <v>5.39696</v>
+        <v>5.5048992</v>
       </c>
       <c r="N52">
-        <v>7.129706666666667</v>
+        <v>7.021767466666668</v>
       </c>
       <c r="O52">
-        <v>0.8912133333333334</v>
+        <v>0.8777209333333335</v>
       </c>
       <c r="P52">
-        <v>6.238493333333334</v>
+        <v>6.144046533333334</v>
       </c>
       <c r="Q52">
-        <v>9.178493333333334</v>
+        <v>9.084046533333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1450842438567572</v>
+        <v>0.1469753723111716</v>
       </c>
       <c r="T52">
-        <v>1.935234710434108</v>
+        <v>1.972096323966187</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.321059757097823</v>
+        <v>2.275548781468454</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1058436824324741</v>
+        <v>0.1059827429365696</v>
       </c>
       <c r="C53">
-        <v>53.80108905351696</v>
+        <v>52.12401627298688</v>
       </c>
       <c r="D53">
-        <v>109.525089053517</v>
+        <v>109.2720162729869</v>
       </c>
       <c r="E53">
-        <v>31.32400000000001</v>
+        <v>32.748</v>
       </c>
       <c r="F53">
-        <v>72.624</v>
+        <v>74.04799999999999</v>
       </c>
       <c r="G53">
         <v>16.9</v>
@@ -5761,28 +5761,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M53">
-        <v>5.5048992</v>
+        <v>5.612838399999999</v>
       </c>
       <c r="N53">
-        <v>7.021767466666668</v>
+        <v>6.913828266666668</v>
       </c>
       <c r="O53">
-        <v>0.8777209333333335</v>
+        <v>0.8642285333333335</v>
       </c>
       <c r="P53">
-        <v>6.144046533333334</v>
+        <v>6.049599733333334</v>
       </c>
       <c r="Q53">
-        <v>9.084046533333334</v>
+        <v>8.989599733333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1469753723111716</v>
+        <v>0.14894529778452</v>
       </c>
       <c r="T53">
-        <v>1.972096323966187</v>
+        <v>2.010493838062101</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.275548781468454</v>
+        <v>2.231788227978676</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1059827429365696</v>
+        <v>0.1061218034406651</v>
       </c>
       <c r="C54">
-        <v>52.12401627298688</v>
+        <v>50.4481103152779</v>
       </c>
       <c r="D54">
-        <v>109.2720162729869</v>
+        <v>109.0201103152779</v>
       </c>
       <c r="E54">
-        <v>32.748</v>
+        <v>34.172</v>
       </c>
       <c r="F54">
-        <v>74.04799999999999</v>
+        <v>75.47199999999999</v>
       </c>
       <c r="G54">
         <v>16.9</v>
@@ -5843,28 +5843,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M54">
-        <v>5.612838399999999</v>
+        <v>5.7207776</v>
       </c>
       <c r="N54">
-        <v>6.913828266666668</v>
+        <v>6.805889066666667</v>
       </c>
       <c r="O54">
-        <v>0.8642285333333335</v>
+        <v>0.8507361333333334</v>
       </c>
       <c r="P54">
-        <v>6.049599733333334</v>
+        <v>5.955152933333334</v>
       </c>
       <c r="Q54">
-        <v>8.989599733333334</v>
+        <v>8.895152933333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.14894529778452</v>
+        <v>0.1509990498737555</v>
       </c>
       <c r="T54">
-        <v>2.010493838062101</v>
+        <v>2.050525288928055</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.231788227978676</v>
+        <v>2.189679016130022</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1061218034406651</v>
+        <v>0.1062608639447606</v>
       </c>
       <c r="C55">
-        <v>50.4481103152779</v>
+        <v>48.77336312928267</v>
       </c>
       <c r="D55">
-        <v>109.0201103152779</v>
+        <v>108.7693631292827</v>
       </c>
       <c r="E55">
-        <v>34.172</v>
+        <v>35.596</v>
       </c>
       <c r="F55">
-        <v>75.47199999999999</v>
+        <v>76.89599999999999</v>
       </c>
       <c r="G55">
         <v>16.9</v>
@@ -5925,28 +5925,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M55">
-        <v>5.7207776</v>
+        <v>5.8287168</v>
       </c>
       <c r="N55">
-        <v>6.805889066666667</v>
+        <v>6.697949866666668</v>
       </c>
       <c r="O55">
-        <v>0.8507361333333334</v>
+        <v>0.8372437333333335</v>
       </c>
       <c r="P55">
-        <v>5.955152933333334</v>
+        <v>5.860706133333334</v>
       </c>
       <c r="Q55">
-        <v>8.895152933333334</v>
+        <v>8.800706133333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1509990498737555</v>
+        <v>0.1531420955320882</v>
       </c>
       <c r="T55">
-        <v>2.050525288928055</v>
+        <v>2.092297237657746</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.189679016130022</v>
+        <v>2.149129404720207</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1062608639447606</v>
+        <v>0.1063999244488561</v>
       </c>
       <c r="C56">
-        <v>48.77336312928267</v>
+        <v>47.09976673779428</v>
       </c>
       <c r="D56">
-        <v>108.7693631292827</v>
+        <v>108.5197667377943</v>
       </c>
       <c r="E56">
-        <v>35.596</v>
+        <v>37.02</v>
       </c>
       <c r="F56">
-        <v>76.89599999999999</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G56">
         <v>16.9</v>
@@ -6007,28 +6007,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M56">
-        <v>5.8287168</v>
+        <v>5.936656</v>
       </c>
       <c r="N56">
-        <v>6.697949866666668</v>
+        <v>6.590010666666667</v>
       </c>
       <c r="O56">
-        <v>0.8372437333333335</v>
+        <v>0.8237513333333334</v>
       </c>
       <c r="P56">
-        <v>5.860706133333334</v>
+        <v>5.766259333333334</v>
       </c>
       <c r="Q56">
-        <v>8.800706133333334</v>
+        <v>8.706259333333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1531420955320882</v>
+        <v>0.1553803876641246</v>
       </c>
       <c r="T56">
-        <v>2.092297237657746</v>
+        <v>2.13592571744209</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.149129404720207</v>
+        <v>2.110054324634385</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1063999244488561</v>
+        <v>0.1065389849529516</v>
       </c>
       <c r="C57">
-        <v>47.09976673779428</v>
+        <v>45.42731323666032</v>
       </c>
       <c r="D57">
-        <v>108.5197667377943</v>
+        <v>108.2713132366603</v>
       </c>
       <c r="E57">
-        <v>37.02</v>
+        <v>38.44400000000001</v>
       </c>
       <c r="F57">
-        <v>78.31999999999999</v>
+        <v>79.744</v>
       </c>
       <c r="G57">
         <v>16.9</v>
@@ -6089,28 +6089,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M57">
-        <v>5.936656</v>
+        <v>6.044595200000001</v>
       </c>
       <c r="N57">
-        <v>6.590010666666667</v>
+        <v>6.482071466666667</v>
       </c>
       <c r="O57">
-        <v>0.8237513333333334</v>
+        <v>0.8102589333333333</v>
       </c>
       <c r="P57">
-        <v>5.766259333333334</v>
+        <v>5.671812533333333</v>
       </c>
       <c r="Q57">
-        <v>8.706259333333334</v>
+        <v>8.611812533333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1553803876641246</v>
+        <v>0.1577204203476172</v>
       </c>
       <c r="T57">
-        <v>2.13592571744209</v>
+        <v>2.181537309943904</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.110054324634385</v>
+        <v>2.072374783123056</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1065389849529516</v>
+        <v>0.1066780454570471</v>
       </c>
       <c r="C58">
-        <v>45.42731323666032</v>
+        <v>43.75599479394857</v>
       </c>
       <c r="D58">
-        <v>108.2713132366603</v>
+        <v>108.0239947939486</v>
       </c>
       <c r="E58">
-        <v>38.44400000000001</v>
+        <v>39.868</v>
       </c>
       <c r="F58">
-        <v>79.744</v>
+        <v>81.16799999999999</v>
       </c>
       <c r="G58">
         <v>16.9</v>
@@ -6171,28 +6171,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M58">
-        <v>6.044595200000001</v>
+        <v>6.1525344</v>
       </c>
       <c r="N58">
-        <v>6.482071466666667</v>
+        <v>6.374132266666668</v>
       </c>
       <c r="O58">
-        <v>0.8102589333333333</v>
+        <v>0.7967665333333335</v>
       </c>
       <c r="P58">
-        <v>5.671812533333333</v>
+        <v>5.577365733333334</v>
       </c>
       <c r="Q58">
-        <v>8.611812533333334</v>
+        <v>8.517365733333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1577204203476172</v>
+        <v>0.1601692917605746</v>
       </c>
       <c r="T58">
-        <v>2.181537309943904</v>
+        <v>2.229270371864407</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.072374783123056</v>
+        <v>2.036017330787564</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1066780454570471</v>
+        <v>0.1068171059611426</v>
       </c>
       <c r="C59">
-        <v>43.75599479394857</v>
+        <v>42.08580364912397</v>
       </c>
       <c r="D59">
-        <v>108.0239947939486</v>
+        <v>107.777803649124</v>
       </c>
       <c r="E59">
-        <v>39.868</v>
+        <v>41.29200000000001</v>
       </c>
       <c r="F59">
-        <v>81.16799999999999</v>
+        <v>82.592</v>
       </c>
       <c r="G59">
         <v>16.9</v>
@@ -6253,28 +6253,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M59">
-        <v>6.1525344</v>
+        <v>6.2604736</v>
       </c>
       <c r="N59">
-        <v>6.374132266666668</v>
+        <v>6.266193066666667</v>
       </c>
       <c r="O59">
-        <v>0.7967665333333335</v>
+        <v>0.7832741333333334</v>
       </c>
       <c r="P59">
-        <v>5.577365733333334</v>
+        <v>5.482918933333334</v>
       </c>
       <c r="Q59">
-        <v>8.517365733333333</v>
+        <v>8.422918933333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1601692917605746</v>
+        <v>0.1627347760979585</v>
       </c>
       <c r="T59">
-        <v>2.229270371864407</v>
+        <v>2.279276436733506</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.036017330787564</v>
+        <v>2.00091358370502</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1068171059611426</v>
+        <v>0.1142869164652381</v>
       </c>
       <c r="C60">
-        <v>42.08580364912402</v>
+        <v>28.90656905310884</v>
       </c>
       <c r="D60">
-        <v>107.777803649124</v>
+        <v>96.02256905310882</v>
       </c>
       <c r="E60">
-        <v>41.29199999999999</v>
+        <v>42.71599999999999</v>
       </c>
       <c r="F60">
-        <v>82.59199999999998</v>
+        <v>84.01599999999998</v>
       </c>
       <c r="G60">
         <v>16.9</v>
@@ -6335,45 +6335,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M60">
-        <v>6.260473599999999</v>
+        <v>7.561439999999997</v>
       </c>
       <c r="N60">
-        <v>6.266193066666668</v>
+        <v>4.96522666666667</v>
       </c>
       <c r="O60">
-        <v>0.7832741333333335</v>
+        <v>0.6206533333333337</v>
       </c>
       <c r="P60">
-        <v>5.482918933333335</v>
+        <v>4.344573333333337</v>
       </c>
       <c r="Q60">
-        <v>8.422918933333335</v>
+        <v>7.284573333333336</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1627347760979585</v>
+        <v>0.1654254060127757</v>
       </c>
       <c r="T60">
-        <v>2.279276436733505</v>
+        <v>2.33172182184012</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0.125</v>
       </c>
       <c r="W60">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.00091358370502</v>
+        <v>1.656650937740255</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1142869164652381</v>
+        <v>0.1145502269693335</v>
       </c>
       <c r="C61">
-        <v>28.90656905310884</v>
+        <v>27.11480661541979</v>
       </c>
       <c r="D61">
-        <v>96.02256905310882</v>
+        <v>95.65480661541977</v>
       </c>
       <c r="E61">
-        <v>42.71599999999999</v>
+        <v>44.13999999999999</v>
       </c>
       <c r="F61">
-        <v>84.01599999999998</v>
+        <v>85.43999999999998</v>
       </c>
       <c r="G61">
         <v>16.9</v>
@@ -6417,28 +6417,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M61">
-        <v>7.561439999999997</v>
+        <v>7.689599999999999</v>
       </c>
       <c r="N61">
-        <v>4.96522666666667</v>
+        <v>4.837066666666669</v>
       </c>
       <c r="O61">
-        <v>0.6206533333333337</v>
+        <v>0.6046333333333336</v>
       </c>
       <c r="P61">
-        <v>4.344573333333337</v>
+        <v>4.232433333333335</v>
       </c>
       <c r="Q61">
-        <v>7.284573333333336</v>
+        <v>7.172433333333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1654254060127757</v>
+        <v>0.1682505674233339</v>
       </c>
       <c r="T61">
-        <v>2.33172182184012</v>
+        <v>2.386789476202067</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.656650937740255</v>
+        <v>1.629040088777917</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1145502269693335</v>
+        <v>0.1148135374734291</v>
       </c>
       <c r="C62">
-        <v>27.11480661541979</v>
+        <v>25.32585045940819</v>
       </c>
       <c r="D62">
-        <v>95.65480661541977</v>
+        <v>95.28985045940819</v>
       </c>
       <c r="E62">
-        <v>44.13999999999999</v>
+        <v>45.564</v>
       </c>
       <c r="F62">
-        <v>85.43999999999998</v>
+        <v>86.86399999999999</v>
       </c>
       <c r="G62">
         <v>16.9</v>
@@ -6499,28 +6499,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M62">
-        <v>7.689599999999999</v>
+        <v>7.817759999999999</v>
       </c>
       <c r="N62">
-        <v>4.837066666666669</v>
+        <v>4.708906666666668</v>
       </c>
       <c r="O62">
-        <v>0.6046333333333336</v>
+        <v>0.5886133333333335</v>
       </c>
       <c r="P62">
-        <v>4.232433333333335</v>
+        <v>4.120293333333334</v>
       </c>
       <c r="Q62">
-        <v>7.172433333333334</v>
+        <v>7.060293333333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1682505674233339</v>
+        <v>0.1712206089062283</v>
       </c>
       <c r="T62">
-        <v>2.386789476202067</v>
+        <v>2.444681112838985</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.629040088777917</v>
+        <v>1.602334513552049</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1148135374734291</v>
+        <v>0.1150768479775245</v>
       </c>
       <c r="C63">
-        <v>25.32585045940819</v>
+        <v>23.53966858635602</v>
       </c>
       <c r="D63">
-        <v>95.28985045940819</v>
+        <v>94.92766858635601</v>
       </c>
       <c r="E63">
-        <v>45.564</v>
+        <v>46.98799999999999</v>
       </c>
       <c r="F63">
-        <v>86.86399999999999</v>
+        <v>88.28799999999998</v>
       </c>
       <c r="G63">
         <v>16.9</v>
@@ -6581,28 +6581,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M63">
-        <v>7.817759999999999</v>
+        <v>7.945919999999998</v>
       </c>
       <c r="N63">
-        <v>4.708906666666668</v>
+        <v>4.580746666666669</v>
       </c>
       <c r="O63">
-        <v>0.5886133333333335</v>
+        <v>0.5725933333333336</v>
       </c>
       <c r="P63">
-        <v>4.120293333333334</v>
+        <v>4.008153333333335</v>
       </c>
       <c r="Q63">
-        <v>7.060293333333334</v>
+        <v>6.948153333333336</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1712206089062283</v>
+        <v>0.1743469683619067</v>
       </c>
       <c r="T63">
-        <v>2.444681112838985</v>
+        <v>2.505619677719951</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.602334513552049</v>
+        <v>1.576490408494758</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1150768479775245</v>
+        <v>0.11534015848162</v>
       </c>
       <c r="C64">
-        <v>23.53966858635602</v>
+        <v>21.75622948219163</v>
       </c>
       <c r="D64">
-        <v>94.92766858635601</v>
+        <v>94.56822948219163</v>
       </c>
       <c r="E64">
-        <v>46.98799999999999</v>
+        <v>48.412</v>
       </c>
       <c r="F64">
-        <v>88.28799999999998</v>
+        <v>89.71199999999999</v>
       </c>
       <c r="G64">
         <v>16.9</v>
@@ -6663,28 +6663,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M64">
-        <v>7.945919999999998</v>
+        <v>8.074079999999999</v>
       </c>
       <c r="N64">
-        <v>4.580746666666669</v>
+        <v>4.452586666666669</v>
       </c>
       <c r="O64">
-        <v>0.5725933333333336</v>
+        <v>0.5565733333333336</v>
       </c>
       <c r="P64">
-        <v>4.008153333333335</v>
+        <v>3.896013333333335</v>
       </c>
       <c r="Q64">
-        <v>6.948153333333336</v>
+        <v>6.836013333333335</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1743469683619067</v>
+        <v>0.1776423202205947</v>
       </c>
       <c r="T64">
-        <v>2.505619677719951</v>
+        <v>2.569852219080969</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.576490408494758</v>
+        <v>1.551466751217064</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.11534015848162</v>
+        <v>0.1156034689857155</v>
       </c>
       <c r="C65">
-        <v>21.75622948219163</v>
+        <v>19.97550210834909</v>
       </c>
       <c r="D65">
-        <v>94.56822948219163</v>
+        <v>94.21150210834907</v>
       </c>
       <c r="E65">
-        <v>48.412</v>
+        <v>49.83599999999999</v>
       </c>
       <c r="F65">
-        <v>89.71199999999999</v>
+        <v>91.13599999999998</v>
       </c>
       <c r="G65">
         <v>16.9</v>
@@ -6745,28 +6745,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M65">
-        <v>8.074079999999999</v>
+        <v>8.202239999999998</v>
       </c>
       <c r="N65">
-        <v>4.452586666666669</v>
+        <v>4.324426666666669</v>
       </c>
       <c r="O65">
-        <v>0.5565733333333336</v>
+        <v>0.5405533333333337</v>
       </c>
       <c r="P65">
-        <v>3.896013333333335</v>
+        <v>3.783873333333336</v>
       </c>
       <c r="Q65">
-        <v>6.836013333333335</v>
+        <v>6.723873333333335</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1776423202205947</v>
+        <v>0.1811207471825431</v>
       </c>
       <c r="T65">
-        <v>2.569852219080969</v>
+        <v>2.637653234962044</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.551466751217064</v>
+        <v>1.527225083229297</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1156034689857155</v>
+        <v>0.115866779489811</v>
       </c>
       <c r="C66">
-        <v>19.97550210834909</v>
+        <v>18.19745589283333</v>
       </c>
       <c r="D66">
-        <v>94.21150210834907</v>
+        <v>93.85745589283331</v>
       </c>
       <c r="E66">
-        <v>49.83599999999999</v>
+        <v>51.26</v>
       </c>
       <c r="F66">
-        <v>91.13599999999998</v>
+        <v>92.55999999999999</v>
       </c>
       <c r="G66">
         <v>16.9</v>
@@ -6827,28 +6827,28 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M66">
-        <v>8.202239999999998</v>
+        <v>8.330399999999999</v>
       </c>
       <c r="N66">
-        <v>4.324426666666669</v>
+        <v>4.196266666666668</v>
       </c>
       <c r="O66">
-        <v>0.5405533333333337</v>
+        <v>0.5245333333333335</v>
       </c>
       <c r="P66">
-        <v>3.783873333333336</v>
+        <v>3.671733333333335</v>
       </c>
       <c r="Q66">
-        <v>6.723873333333335</v>
+        <v>6.611733333333335</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1811207471825431</v>
+        <v>0.1847979413994601</v>
       </c>
       <c r="T66">
-        <v>2.637653234962044</v>
+        <v>2.709328594607752</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.527225083229297</v>
+        <v>1.503729312718077</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.115866779489811</v>
+        <v>0.1504492488196119</v>
       </c>
       <c r="C67">
-        <v>18.19745589283333</v>
+        <v>-14.24274944450265</v>
       </c>
       <c r="D67">
-        <v>93.85745589283331</v>
+        <v>62.84125055549734</v>
       </c>
       <c r="E67">
-        <v>51.26</v>
+        <v>52.684</v>
       </c>
       <c r="F67">
-        <v>92.55999999999999</v>
+        <v>93.98399999999999</v>
       </c>
       <c r="G67">
         <v>16.9</v>
@@ -6909,45 +6909,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M67">
-        <v>8.330399999999999</v>
+        <v>13.7968512</v>
       </c>
       <c r="N67">
-        <v>4.196266666666668</v>
+        <v>-1.270184533333333</v>
       </c>
       <c r="O67">
-        <v>0.5245333333333335</v>
+        <v>-0.1587730666666667</v>
       </c>
       <c r="P67">
-        <v>3.671733333333335</v>
+        <v>-1.111411466666667</v>
       </c>
       <c r="Q67">
-        <v>6.611733333333335</v>
+        <v>1.828588533333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1847979413994601</v>
+        <v>0.1898743218201849</v>
       </c>
       <c r="T67">
-        <v>2.709328594607752</v>
+        <v>2.808276697669586</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.125</v>
+        <v>0.1134920795067597</v>
       </c>
       <c r="W67">
-        <v>0.07875</v>
+        <v>0.1301393627284077</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.503729312718077</v>
+        <v>0.9079366360540778</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1504492488196119</v>
+        <v>0.1514592488196119</v>
       </c>
       <c r="C68">
-        <v>-14.24274944450265</v>
+        <v>-16.26745088588248</v>
       </c>
       <c r="D68">
-        <v>62.84125055549734</v>
+        <v>62.2405491141175</v>
       </c>
       <c r="E68">
-        <v>52.684</v>
+        <v>54.108</v>
       </c>
       <c r="F68">
-        <v>93.98399999999999</v>
+        <v>95.40799999999999</v>
       </c>
       <c r="G68">
         <v>16.9</v>
@@ -6991,37 +6991,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M68">
-        <v>13.7968512</v>
+        <v>14.0058944</v>
       </c>
       <c r="N68">
-        <v>-1.270184533333333</v>
+        <v>-1.479227733333332</v>
       </c>
       <c r="O68">
-        <v>-0.1587730666666667</v>
+        <v>-0.1849034666666665</v>
       </c>
       <c r="P68">
-        <v>-1.111411466666667</v>
+        <v>-1.294324266666665</v>
       </c>
       <c r="Q68">
-        <v>1.828588533333333</v>
+        <v>1.645675733333335</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1898743218201849</v>
+        <v>0.1942402103601905</v>
       </c>
       <c r="T68">
-        <v>2.808276697669586</v>
+        <v>2.893375991538362</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1134920795067597</v>
+        <v>0.1117981678723305</v>
       </c>
       <c r="W68">
-        <v>0.1301393627284077</v>
+        <v>0.1303880289563419</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9079366360540778</v>
+        <v>0.8943853429786439</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1514592488196119</v>
+        <v>0.1524692488196119</v>
       </c>
       <c r="C69">
-        <v>-16.26745088588248</v>
+        <v>-18.28077681909092</v>
       </c>
       <c r="D69">
-        <v>62.2405491141175</v>
+        <v>61.65122318090908</v>
       </c>
       <c r="E69">
-        <v>54.108</v>
+        <v>55.532</v>
       </c>
       <c r="F69">
-        <v>95.40799999999999</v>
+        <v>96.83199999999999</v>
       </c>
       <c r="G69">
         <v>16.9</v>
@@ -7073,37 +7073,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M69">
-        <v>14.0058944</v>
+        <v>14.2149376</v>
       </c>
       <c r="N69">
-        <v>-1.479227733333332</v>
+        <v>-1.688270933333333</v>
       </c>
       <c r="O69">
-        <v>-0.1849034666666665</v>
+        <v>-0.2110338666666667</v>
       </c>
       <c r="P69">
-        <v>-1.294324266666665</v>
+        <v>-1.477237066666667</v>
       </c>
       <c r="Q69">
-        <v>1.645675733333335</v>
+        <v>1.462762933333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1942402103601905</v>
+        <v>0.1988789669339464</v>
       </c>
       <c r="T69">
-        <v>2.893375991538362</v>
+        <v>2.983793991273936</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1117981678723305</v>
+        <v>0.1101540771683256</v>
       </c>
       <c r="W69">
-        <v>0.1303880289563419</v>
+        <v>0.1306293814716898</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8943853429786439</v>
+        <v>0.881232617346605</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1524692488196119</v>
+        <v>0.1534792488196119</v>
       </c>
       <c r="C70">
-        <v>-18.28077681909092</v>
+        <v>-20.28304734099093</v>
       </c>
       <c r="D70">
-        <v>61.65122318090908</v>
+        <v>61.07295265900905</v>
       </c>
       <c r="E70">
-        <v>55.532</v>
+        <v>56.956</v>
       </c>
       <c r="F70">
-        <v>96.83199999999999</v>
+        <v>98.25599999999999</v>
       </c>
       <c r="G70">
         <v>16.9</v>
@@ -7155,37 +7155,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M70">
-        <v>14.2149376</v>
+        <v>14.4239808</v>
       </c>
       <c r="N70">
-        <v>-1.688270933333333</v>
+        <v>-1.897314133333332</v>
       </c>
       <c r="O70">
-        <v>-0.2110338666666667</v>
+        <v>-0.2371642666666665</v>
       </c>
       <c r="P70">
-        <v>-1.477237066666667</v>
+        <v>-1.660149866666665</v>
       </c>
       <c r="Q70">
-        <v>1.462762933333333</v>
+        <v>1.279850133333335</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1988789669339464</v>
+        <v>0.2038169981253641</v>
       </c>
       <c r="T70">
-        <v>2.983793991273936</v>
+        <v>3.080045410347289</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1101540771683256</v>
+        <v>0.1085576412673354</v>
       </c>
       <c r="W70">
-        <v>0.1306293814716898</v>
+        <v>0.1308637382619552</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.881232617346605</v>
+        <v>0.8684611301386832</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1534792488196119</v>
+        <v>0.1544892488196119</v>
       </c>
       <c r="C71">
-        <v>-20.28304734099093</v>
+        <v>-22.27457065038442</v>
       </c>
       <c r="D71">
-        <v>61.07295265900905</v>
+        <v>60.50542934961558</v>
       </c>
       <c r="E71">
-        <v>56.956</v>
+        <v>58.38</v>
       </c>
       <c r="F71">
-        <v>98.25599999999999</v>
+        <v>99.67999999999999</v>
       </c>
       <c r="G71">
         <v>16.9</v>
@@ -7237,37 +7237,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M71">
-        <v>14.4239808</v>
+        <v>14.633024</v>
       </c>
       <c r="N71">
-        <v>-1.897314133333332</v>
+        <v>-2.106357333333333</v>
       </c>
       <c r="O71">
-        <v>-0.2371642666666665</v>
+        <v>-0.2632946666666667</v>
       </c>
       <c r="P71">
-        <v>-1.660149866666665</v>
+        <v>-1.843062666666667</v>
       </c>
       <c r="Q71">
-        <v>1.279850133333335</v>
+        <v>1.096937333333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2038169981253641</v>
+        <v>0.2090842313962095</v>
       </c>
       <c r="T71">
-        <v>3.080045410347289</v>
+        <v>3.182713590692198</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1085576412673354</v>
+        <v>0.1070068178206592</v>
       </c>
       <c r="W71">
-        <v>0.1308637382619552</v>
+        <v>0.1310913991439273</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8684611301386832</v>
+        <v>0.8560545425652734</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1544892488196119</v>
+        <v>0.1554992488196119</v>
       </c>
       <c r="C72">
-        <v>-22.27457065038442</v>
+        <v>-24.25564359573887</v>
       </c>
       <c r="D72">
-        <v>60.50542934961558</v>
+        <v>59.94835640426113</v>
       </c>
       <c r="E72">
-        <v>58.38</v>
+        <v>59.80400000000001</v>
       </c>
       <c r="F72">
-        <v>99.67999999999999</v>
+        <v>101.104</v>
       </c>
       <c r="G72">
         <v>16.9</v>
@@ -7319,37 +7319,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M72">
-        <v>14.633024</v>
+        <v>14.8420672</v>
       </c>
       <c r="N72">
-        <v>-2.106357333333333</v>
+        <v>-2.315400533333333</v>
       </c>
       <c r="O72">
-        <v>-0.2632946666666667</v>
+        <v>-0.2894250666666667</v>
       </c>
       <c r="P72">
-        <v>-1.843062666666667</v>
+        <v>-2.025975466666667</v>
       </c>
       <c r="Q72">
-        <v>1.096937333333333</v>
+        <v>0.914024533333333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2090842313962095</v>
+        <v>0.2147147221340099</v>
       </c>
       <c r="T72">
-        <v>3.182713590692198</v>
+        <v>3.292462335198826</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1070068178206592</v>
+        <v>0.105499679541495</v>
       </c>
       <c r="W72">
-        <v>0.1310913991439273</v>
+        <v>0.1313126470433086</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8560545425652734</v>
+        <v>0.8439974363319597</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1554992488196119</v>
+        <v>0.1565092488196119</v>
       </c>
       <c r="C73">
-        <v>-24.25564359573886</v>
+        <v>-26.22655219293257</v>
       </c>
       <c r="D73">
-        <v>59.94835640426113</v>
+        <v>59.40144780706741</v>
       </c>
       <c r="E73">
-        <v>59.80399999999999</v>
+        <v>61.22799999999999</v>
       </c>
       <c r="F73">
-        <v>101.104</v>
+        <v>102.528</v>
       </c>
       <c r="G73">
         <v>16.9</v>
@@ -7401,37 +7401,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M73">
-        <v>14.8420672</v>
+        <v>15.0511104</v>
       </c>
       <c r="N73">
-        <v>-2.315400533333332</v>
+        <v>-2.524443733333332</v>
       </c>
       <c r="O73">
-        <v>-0.2894250666666665</v>
+        <v>-0.3155554666666665</v>
       </c>
       <c r="P73">
-        <v>-2.025975466666665</v>
+        <v>-2.208888266666665</v>
       </c>
       <c r="Q73">
-        <v>0.9140245333333348</v>
+        <v>0.7311117333333348</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2147147221340098</v>
+        <v>0.220747390781653</v>
       </c>
       <c r="T73">
-        <v>3.292462335198825</v>
+        <v>3.41005027574164</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.105499679541495</v>
+        <v>0.1040344062145298</v>
       </c>
       <c r="W73">
-        <v>0.1313126470433086</v>
+        <v>0.131527749167707</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8439974363319598</v>
+        <v>0.8322752497162381</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1565092488196119</v>
+        <v>0.1575192488196119</v>
       </c>
       <c r="C74">
-        <v>-26.22655219293257</v>
+        <v>-28.18757211491584</v>
       </c>
       <c r="D74">
-        <v>59.40144780706741</v>
+        <v>58.86442788508415</v>
       </c>
       <c r="E74">
-        <v>61.22799999999999</v>
+        <v>62.65199999999999</v>
       </c>
       <c r="F74">
-        <v>102.528</v>
+        <v>103.952</v>
       </c>
       <c r="G74">
         <v>16.9</v>
@@ -7483,37 +7483,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M74">
-        <v>15.0511104</v>
+        <v>15.2601536</v>
       </c>
       <c r="N74">
-        <v>-2.524443733333332</v>
+        <v>-2.733486933333332</v>
       </c>
       <c r="O74">
-        <v>-0.3155554666666665</v>
+        <v>-0.3416858666666664</v>
       </c>
       <c r="P74">
-        <v>-2.208888266666665</v>
+        <v>-2.391801066666665</v>
       </c>
       <c r="Q74">
-        <v>0.7311117333333348</v>
+        <v>0.5481989333333348</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.220747390781653</v>
+        <v>0.2272269237735661</v>
       </c>
       <c r="T74">
-        <v>3.41005027574164</v>
+        <v>3.536348434102441</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1040344062145298</v>
+        <v>0.1026092773622759</v>
       </c>
       <c r="W74">
-        <v>0.131527749167707</v>
+        <v>0.1317369580832179</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8322752497162381</v>
+        <v>0.8208742188982074</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1575192488196119</v>
+        <v>0.1585292488196119</v>
       </c>
       <c r="C75">
-        <v>-28.18757211491584</v>
+        <v>-30.13896915504932</v>
       </c>
       <c r="D75">
-        <v>58.86442788508415</v>
+        <v>58.33703084495065</v>
       </c>
       <c r="E75">
-        <v>62.65199999999999</v>
+        <v>64.07599999999999</v>
       </c>
       <c r="F75">
-        <v>103.952</v>
+        <v>105.376</v>
       </c>
       <c r="G75">
         <v>16.9</v>
@@ -7565,37 +7565,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M75">
-        <v>15.2601536</v>
+        <v>15.4691968</v>
       </c>
       <c r="N75">
-        <v>-2.733486933333332</v>
+        <v>-2.942530133333332</v>
       </c>
       <c r="O75">
-        <v>-0.3416858666666664</v>
+        <v>-0.3678162666666664</v>
       </c>
       <c r="P75">
-        <v>-2.391801066666665</v>
+        <v>-2.574713866666665</v>
       </c>
       <c r="Q75">
-        <v>0.5481989333333348</v>
+        <v>0.3652861333333348</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2272269237735661</v>
+        <v>0.2342048823802417</v>
       </c>
       <c r="T75">
-        <v>3.536348434102441</v>
+        <v>3.672361835414074</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1026092773622759</v>
+        <v>0.101222665506029</v>
       </c>
       <c r="W75">
-        <v>0.1317369580832179</v>
+        <v>0.131940512703715</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8208742188982074</v>
+        <v>0.8097813240482317</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1585292488196119</v>
+        <v>0.2011058906246718</v>
       </c>
       <c r="C76">
-        <v>-30.13896915504932</v>
+        <v>-47.55589032671814</v>
       </c>
       <c r="D76">
-        <v>58.33703084495065</v>
+        <v>42.34410967328184</v>
       </c>
       <c r="E76">
-        <v>64.07599999999999</v>
+        <v>65.5</v>
       </c>
       <c r="F76">
-        <v>105.376</v>
+        <v>106.8</v>
       </c>
       <c r="G76">
         <v>16.9</v>
@@ -7647,45 +7647,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M76">
-        <v>15.4691968</v>
+        <v>21.44544</v>
       </c>
       <c r="N76">
-        <v>-2.942530133333332</v>
+        <v>-8.918773333333331</v>
       </c>
       <c r="O76">
-        <v>-0.3678162666666664</v>
+        <v>-1.114846666666666</v>
       </c>
       <c r="P76">
-        <v>-2.574713866666665</v>
+        <v>-7.803926666666664</v>
       </c>
       <c r="Q76">
-        <v>0.3652861333333348</v>
+        <v>-4.863926666666664</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2342048823802417</v>
+        <v>0.2460076448956907</v>
       </c>
       <c r="T76">
-        <v>3.672361835414074</v>
+        <v>3.902419645310492</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.101222665506029</v>
+        <v>0.07301474501494647</v>
       </c>
       <c r="W76">
-        <v>0.131940512703715</v>
+        <v>0.1861386392009988</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8097813240482317</v>
+        <v>0.5841179601195717</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2011058906246718</v>
+        <v>0.2026558906246717</v>
       </c>
       <c r="C77">
-        <v>-47.55589032671814</v>
+        <v>-49.39832134471946</v>
       </c>
       <c r="D77">
-        <v>42.34410967328184</v>
+        <v>41.92567865528053</v>
       </c>
       <c r="E77">
-        <v>65.5</v>
+        <v>66.92400000000001</v>
       </c>
       <c r="F77">
-        <v>106.8</v>
+        <v>108.224</v>
       </c>
       <c r="G77">
         <v>16.9</v>
@@ -7729,37 +7729,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M77">
-        <v>21.44544</v>
+        <v>21.7313792</v>
       </c>
       <c r="N77">
-        <v>-8.918773333333331</v>
+        <v>-9.204712533333332</v>
       </c>
       <c r="O77">
-        <v>-1.114846666666666</v>
+        <v>-1.150589066666666</v>
       </c>
       <c r="P77">
-        <v>-7.803926666666664</v>
+        <v>-8.054123466666665</v>
       </c>
       <c r="Q77">
-        <v>-4.863926666666664</v>
+        <v>-5.114123466666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2460076448956907</v>
+        <v>0.2543496300996778</v>
       </c>
       <c r="T77">
-        <v>3.902419645310492</v>
+        <v>4.065020463865096</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07301474501494647</v>
+        <v>0.07205402468580244</v>
       </c>
       <c r="W77">
-        <v>0.1861386392009988</v>
+        <v>0.1863315518430909</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5841179601195717</v>
+        <v>0.5764321974864195</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2026558906246717</v>
+        <v>0.2042058906246718</v>
       </c>
       <c r="C78">
-        <v>-49.39832134471946</v>
+        <v>-51.2325636763614</v>
       </c>
       <c r="D78">
-        <v>41.92567865528053</v>
+        <v>41.51543632363858</v>
       </c>
       <c r="E78">
-        <v>66.92400000000001</v>
+        <v>68.34799999999998</v>
       </c>
       <c r="F78">
-        <v>108.224</v>
+        <v>109.648</v>
       </c>
       <c r="G78">
         <v>16.9</v>
@@ -7811,37 +7811,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M78">
-        <v>21.7313792</v>
+        <v>22.0173184</v>
       </c>
       <c r="N78">
-        <v>-9.204712533333332</v>
+        <v>-9.49065173333333</v>
       </c>
       <c r="O78">
-        <v>-1.150589066666666</v>
+        <v>-1.186331466666666</v>
       </c>
       <c r="P78">
-        <v>-8.054123466666665</v>
+        <v>-8.304320266666664</v>
       </c>
       <c r="Q78">
-        <v>-5.114123466666666</v>
+        <v>-5.364320266666665</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2543496300996778</v>
+        <v>0.263417005321403</v>
       </c>
       <c r="T78">
-        <v>4.065020463865096</v>
+        <v>4.241760484033144</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07205402468580244</v>
+        <v>0.07111825813144136</v>
       </c>
       <c r="W78">
-        <v>0.1863315518430909</v>
+        <v>0.1865194537672066</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5764321974864195</v>
+        <v>0.568946065051531</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2042058906246718</v>
+        <v>0.2057558906246717</v>
       </c>
       <c r="C79">
-        <v>-51.2325636763614</v>
+        <v>-53.05885537096758</v>
       </c>
       <c r="D79">
-        <v>41.51543632363858</v>
+        <v>41.1131446290324</v>
       </c>
       <c r="E79">
-        <v>68.34799999999998</v>
+        <v>69.77199999999999</v>
       </c>
       <c r="F79">
-        <v>109.648</v>
+        <v>111.072</v>
       </c>
       <c r="G79">
         <v>16.9</v>
@@ -7893,37 +7893,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M79">
-        <v>22.0173184</v>
+        <v>22.3032576</v>
       </c>
       <c r="N79">
-        <v>-9.49065173333333</v>
+        <v>-9.776590933333331</v>
       </c>
       <c r="O79">
-        <v>-1.186331466666666</v>
+        <v>-1.222073866666666</v>
       </c>
       <c r="P79">
-        <v>-8.304320266666664</v>
+        <v>-8.554517066666666</v>
       </c>
       <c r="Q79">
-        <v>-5.364320266666665</v>
+        <v>-5.614517066666666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.263417005321403</v>
+        <v>0.2733086873814667</v>
       </c>
       <c r="T79">
-        <v>4.241760484033144</v>
+        <v>4.434567778761923</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07111825813144136</v>
+        <v>0.07020648559129468</v>
       </c>
       <c r="W79">
-        <v>0.1865194537672066</v>
+        <v>0.186702537693268</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.568946065051531</v>
+        <v>0.5616518847303574</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2057558906246717</v>
+        <v>0.2073058906246718</v>
       </c>
       <c r="C80">
-        <v>-53.05885537096758</v>
+        <v>-54.87742533945928</v>
       </c>
       <c r="D80">
-        <v>41.1131446290324</v>
+        <v>40.7185746605407</v>
       </c>
       <c r="E80">
-        <v>69.77199999999999</v>
+        <v>71.196</v>
       </c>
       <c r="F80">
-        <v>111.072</v>
+        <v>112.496</v>
       </c>
       <c r="G80">
         <v>16.9</v>
@@ -7975,37 +7975,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M80">
-        <v>22.3032576</v>
+        <v>22.5891968</v>
       </c>
       <c r="N80">
-        <v>-9.776590933333331</v>
+        <v>-10.06253013333333</v>
       </c>
       <c r="O80">
-        <v>-1.222073866666666</v>
+        <v>-1.257816266666666</v>
       </c>
       <c r="P80">
-        <v>-8.554517066666666</v>
+        <v>-8.804713866666663</v>
       </c>
       <c r="Q80">
-        <v>-5.614517066666666</v>
+        <v>-5.864713866666664</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2733086873814667</v>
+        <v>0.2841424343996318</v>
       </c>
       <c r="T80">
-        <v>4.434567778761923</v>
+        <v>4.645737672988682</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07020648559129468</v>
+        <v>0.06931779590026564</v>
       </c>
       <c r="W80">
-        <v>0.186702537693268</v>
+        <v>0.1868809865832267</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5616518847303574</v>
+        <v>0.5545423672021251</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2073058906246718</v>
+        <v>0.2088558906246717</v>
       </c>
       <c r="C81">
-        <v>-54.87742533945928</v>
+        <v>-56.68849378870113</v>
       </c>
       <c r="D81">
-        <v>40.7185746605407</v>
+        <v>40.33150621129886</v>
       </c>
       <c r="E81">
-        <v>71.196</v>
+        <v>72.62</v>
       </c>
       <c r="F81">
-        <v>112.496</v>
+        <v>113.92</v>
       </c>
       <c r="G81">
         <v>16.9</v>
@@ -8057,37 +8057,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M81">
-        <v>22.5891968</v>
+        <v>22.875136</v>
       </c>
       <c r="N81">
-        <v>-10.06253013333333</v>
+        <v>-10.34846933333333</v>
       </c>
       <c r="O81">
-        <v>-1.257816266666666</v>
+        <v>-1.293558666666666</v>
       </c>
       <c r="P81">
-        <v>-8.804713866666663</v>
+        <v>-9.054910666666665</v>
       </c>
       <c r="Q81">
-        <v>-5.864713866666664</v>
+        <v>-6.114910666666665</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2841424343996318</v>
+        <v>0.2960595561196134</v>
       </c>
       <c r="T81">
-        <v>4.645737672988682</v>
+        <v>4.878024556638116</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.06931779590026564</v>
+        <v>0.06845132345151231</v>
       </c>
       <c r="W81">
-        <v>0.1868809865832267</v>
+        <v>0.1870549742509363</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5545423672021251</v>
+        <v>0.5476105876120985</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2088558906246717</v>
+        <v>0.2104058906246717</v>
       </c>
       <c r="C82">
-        <v>-56.68849378870113</v>
+        <v>-58.4922726313068</v>
       </c>
       <c r="D82">
-        <v>40.33150621129886</v>
+        <v>39.9517273686932</v>
       </c>
       <c r="E82">
-        <v>72.62</v>
+        <v>74.04400000000001</v>
       </c>
       <c r="F82">
-        <v>113.92</v>
+        <v>115.344</v>
       </c>
       <c r="G82">
         <v>16.9</v>
@@ -8139,37 +8139,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M82">
-        <v>22.875136</v>
+        <v>23.1610752</v>
       </c>
       <c r="N82">
-        <v>-10.34846933333333</v>
+        <v>-10.63440853333333</v>
       </c>
       <c r="O82">
-        <v>-1.293558666666666</v>
+        <v>-1.329301066666666</v>
       </c>
       <c r="P82">
-        <v>-9.054910666666665</v>
+        <v>-9.305107466666666</v>
       </c>
       <c r="Q82">
-        <v>-6.114910666666665</v>
+        <v>-6.365107466666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2960595561196134</v>
+        <v>0.3092311117048562</v>
       </c>
       <c r="T82">
-        <v>4.878024556638116</v>
+        <v>5.134762691198016</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.06845132345151231</v>
+        <v>0.06760624538420969</v>
       </c>
       <c r="W82">
-        <v>0.1870549742509363</v>
+        <v>0.1872246659268507</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5476105876120985</v>
+        <v>0.5408499630736775</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2104058906246717</v>
+        <v>0.2119558906246717</v>
       </c>
       <c r="C83">
-        <v>-58.4922726313068</v>
+        <v>-60.28896587250735</v>
       </c>
       <c r="D83">
-        <v>39.9517273686932</v>
+        <v>39.57903412749263</v>
       </c>
       <c r="E83">
-        <v>74.04400000000001</v>
+        <v>75.46799999999999</v>
       </c>
       <c r="F83">
-        <v>115.344</v>
+        <v>116.768</v>
       </c>
       <c r="G83">
         <v>16.9</v>
@@ -8221,37 +8221,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M83">
-        <v>23.1610752</v>
+        <v>23.4470144</v>
       </c>
       <c r="N83">
-        <v>-10.63440853333333</v>
+        <v>-10.92034773333333</v>
       </c>
       <c r="O83">
-        <v>-1.329301066666666</v>
+        <v>-1.365043466666666</v>
       </c>
       <c r="P83">
-        <v>-9.305107466666666</v>
+        <v>-9.555304266666663</v>
       </c>
       <c r="Q83">
-        <v>-6.365107466666666</v>
+        <v>-6.615304266666664</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3092311117048562</v>
+        <v>0.3238661734662372</v>
       </c>
       <c r="T83">
-        <v>5.134762691198016</v>
+        <v>5.420027285153463</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.06760624538420969</v>
+        <v>0.06678177897708519</v>
       </c>
       <c r="W83">
-        <v>0.1872246659268507</v>
+        <v>0.1873902187814013</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5408499630736775</v>
+        <v>0.5342542318166814</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2119558906246717</v>
+        <v>0.2135058906246718</v>
       </c>
       <c r="C84">
-        <v>-60.28896587250735</v>
+        <v>-62.07876997556603</v>
       </c>
       <c r="D84">
-        <v>39.57903412749263</v>
+        <v>39.21323002443396</v>
       </c>
       <c r="E84">
-        <v>75.46799999999999</v>
+        <v>76.892</v>
       </c>
       <c r="F84">
-        <v>116.768</v>
+        <v>118.192</v>
       </c>
       <c r="G84">
         <v>16.9</v>
@@ -8303,37 +8303,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M84">
-        <v>23.4470144</v>
+        <v>23.7329536</v>
       </c>
       <c r="N84">
-        <v>-10.92034773333333</v>
+        <v>-11.20628693333333</v>
       </c>
       <c r="O84">
-        <v>-1.365043466666666</v>
+        <v>-1.400785866666666</v>
       </c>
       <c r="P84">
-        <v>-9.555304266666663</v>
+        <v>-9.805501066666665</v>
       </c>
       <c r="Q84">
-        <v>-6.615304266666664</v>
+        <v>-6.865501066666665</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3238661734662372</v>
+        <v>0.3402230071995453</v>
       </c>
       <c r="T84">
-        <v>5.420027285153463</v>
+        <v>5.738852419574256</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.06678177897708519</v>
+        <v>0.06597717923037331</v>
       </c>
       <c r="W84">
-        <v>0.1873902187814013</v>
+        <v>0.187551782410541</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5342542318166814</v>
+        <v>0.5278174338429865</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2135058906246718</v>
+        <v>0.2150558906246717</v>
       </c>
       <c r="C85">
-        <v>-62.07876997556603</v>
+        <v>-63.86187420711477</v>
       </c>
       <c r="D85">
-        <v>39.21323002443396</v>
+        <v>38.85412579288521</v>
       </c>
       <c r="E85">
-        <v>76.892</v>
+        <v>78.316</v>
       </c>
       <c r="F85">
-        <v>118.192</v>
+        <v>119.616</v>
       </c>
       <c r="G85">
         <v>16.9</v>
@@ -8385,37 +8385,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M85">
-        <v>23.7329536</v>
+        <v>24.0188928</v>
       </c>
       <c r="N85">
-        <v>-11.20628693333333</v>
+        <v>-11.49222613333333</v>
       </c>
       <c r="O85">
-        <v>-1.400785866666666</v>
+        <v>-1.436528266666666</v>
       </c>
       <c r="P85">
-        <v>-9.805501066666665</v>
+        <v>-10.05569786666666</v>
       </c>
       <c r="Q85">
-        <v>-6.865501066666665</v>
+        <v>-7.115697866666663</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3402230071995453</v>
+        <v>0.3586244451495169</v>
       </c>
       <c r="T85">
-        <v>5.738852419574256</v>
+        <v>6.097530695797647</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.06597717923037331</v>
+        <v>0.06519173662048793</v>
       </c>
       <c r="W85">
-        <v>0.187551782410541</v>
+        <v>0.187709499286606</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5278174338429865</v>
+        <v>0.5215338929639033</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2150558906246717</v>
+        <v>0.2166058906246717</v>
       </c>
       <c r="C86">
-        <v>-63.86187420711476</v>
+        <v>-65.63846096368809</v>
       </c>
       <c r="D86">
-        <v>38.85412579288521</v>
+        <v>38.50153903631188</v>
       </c>
       <c r="E86">
-        <v>78.31599999999997</v>
+        <v>79.73999999999998</v>
       </c>
       <c r="F86">
-        <v>119.616</v>
+        <v>121.04</v>
       </c>
       <c r="G86">
         <v>16.9</v>
@@ -8467,37 +8467,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M86">
-        <v>24.0188928</v>
+        <v>24.304832</v>
       </c>
       <c r="N86">
-        <v>-11.49222613333333</v>
+        <v>-11.77816533333333</v>
       </c>
       <c r="O86">
-        <v>-1.436528266666666</v>
+        <v>-1.472270666666666</v>
       </c>
       <c r="P86">
-        <v>-10.05569786666666</v>
+        <v>-10.30589466666666</v>
       </c>
       <c r="Q86">
-        <v>-7.115697866666663</v>
+        <v>-7.365894666666664</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3586244451495167</v>
+        <v>0.3794794081594845</v>
       </c>
       <c r="T86">
-        <v>6.097530695797643</v>
+        <v>6.504032742184153</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.06519173662048793</v>
+        <v>0.06442477501318807</v>
       </c>
       <c r="W86">
-        <v>0.187709499286606</v>
+        <v>0.1878635051773518</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5215338929639033</v>
+        <v>0.5153982001055044</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2166058906246717</v>
+        <v>0.2181558906246717</v>
       </c>
       <c r="C87">
-        <v>-65.63846096368809</v>
+        <v>-67.40870608063764</v>
       </c>
       <c r="D87">
-        <v>38.50153903631188</v>
+        <v>38.15529391936234</v>
       </c>
       <c r="E87">
-        <v>79.73999999999998</v>
+        <v>81.16399999999999</v>
       </c>
       <c r="F87">
-        <v>121.04</v>
+        <v>122.464</v>
       </c>
       <c r="G87">
         <v>16.9</v>
@@ -8549,37 +8549,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M87">
-        <v>24.304832</v>
+        <v>24.5907712</v>
       </c>
       <c r="N87">
-        <v>-11.77816533333333</v>
+        <v>-12.06410453333333</v>
       </c>
       <c r="O87">
-        <v>-1.472270666666666</v>
+        <v>-1.508013066666666</v>
       </c>
       <c r="P87">
-        <v>-10.30589466666666</v>
+        <v>-10.55609146666666</v>
       </c>
       <c r="Q87">
-        <v>-7.365894666666664</v>
+        <v>-7.616091466666665</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3794794081594845</v>
+        <v>0.4033136515994477</v>
       </c>
       <c r="T87">
-        <v>6.504032742184153</v>
+        <v>6.968606509483021</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.06442477501318807</v>
+        <v>0.06367564972233704</v>
       </c>
       <c r="W87">
-        <v>0.1878635051773518</v>
+        <v>0.1880139295357547</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5153982001055044</v>
+        <v>0.5094051977786962</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2181558906246717</v>
+        <v>0.2197058906246717</v>
       </c>
       <c r="C88">
-        <v>-67.40870608063764</v>
+        <v>-69.17277912452695</v>
       </c>
       <c r="D88">
-        <v>38.15529391936234</v>
+        <v>37.81522087547302</v>
       </c>
       <c r="E88">
-        <v>81.16399999999999</v>
+        <v>82.58799999999999</v>
       </c>
       <c r="F88">
-        <v>122.464</v>
+        <v>123.888</v>
       </c>
       <c r="G88">
         <v>16.9</v>
@@ -8631,37 +8631,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M88">
-        <v>24.5907712</v>
+        <v>24.8767104</v>
       </c>
       <c r="N88">
-        <v>-12.06410453333333</v>
+        <v>-12.35004373333333</v>
       </c>
       <c r="O88">
-        <v>-1.508013066666666</v>
+        <v>-1.543755466666666</v>
       </c>
       <c r="P88">
-        <v>-10.55609146666666</v>
+        <v>-10.80628826666666</v>
       </c>
       <c r="Q88">
-        <v>-7.616091466666665</v>
+        <v>-7.866288266666663</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4033136515994477</v>
+        <v>0.4308147017224821</v>
       </c>
       <c r="T88">
-        <v>6.968606509483021</v>
+        <v>7.504653164058638</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.06367564972233704</v>
+        <v>0.06294374570254006</v>
       </c>
       <c r="W88">
-        <v>0.1880139295357547</v>
+        <v>0.18816089586293</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5094051977786962</v>
+        <v>0.5035499656203205</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2197058906246717</v>
+        <v>0.2524862934766177</v>
       </c>
       <c r="C89">
-        <v>-69.17277912452695</v>
+        <v>-76.59426523442983</v>
       </c>
       <c r="D89">
-        <v>37.81522087547302</v>
+        <v>31.81773476557015</v>
       </c>
       <c r="E89">
-        <v>82.58799999999999</v>
+        <v>84.012</v>
       </c>
       <c r="F89">
-        <v>123.888</v>
+        <v>125.312</v>
       </c>
       <c r="G89">
         <v>16.9</v>
@@ -8713,45 +8713,45 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M89">
-        <v>24.8767104</v>
+        <v>29.5485696</v>
       </c>
       <c r="N89">
-        <v>-12.35004373333333</v>
+        <v>-17.02190293333333</v>
       </c>
       <c r="O89">
-        <v>-1.543755466666666</v>
+        <v>-2.127737866666666</v>
       </c>
       <c r="P89">
-        <v>-10.80628826666666</v>
+        <v>-14.89416506666666</v>
       </c>
       <c r="Q89">
-        <v>-7.866288266666663</v>
+        <v>-11.95416506666666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4308147017224821</v>
+        <v>0.4664859506322381</v>
       </c>
       <c r="T89">
-        <v>7.504653164058638</v>
+        <v>8.199952200170463</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06294374570254006</v>
+        <v>0.05299184882821988</v>
       </c>
       <c r="W89">
-        <v>0.18816089586293</v>
+        <v>0.2233045220463058</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5035499656203205</v>
+        <v>0.423934790625759</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2524862934766177</v>
+        <v>0.2543862934766176</v>
       </c>
       <c r="C90">
-        <v>-76.59426523442983</v>
+        <v>-78.30809106644864</v>
       </c>
       <c r="D90">
-        <v>31.81773476557015</v>
+        <v>31.52790893355134</v>
       </c>
       <c r="E90">
-        <v>84.012</v>
+        <v>85.43599999999998</v>
       </c>
       <c r="F90">
-        <v>125.312</v>
+        <v>126.736</v>
       </c>
       <c r="G90">
         <v>16.9</v>
@@ -8795,37 +8795,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M90">
-        <v>29.5485696</v>
+        <v>29.88434879999999</v>
       </c>
       <c r="N90">
-        <v>-17.02190293333333</v>
+        <v>-17.35768213333333</v>
       </c>
       <c r="O90">
-        <v>-2.127737866666666</v>
+        <v>-2.169710266666666</v>
       </c>
       <c r="P90">
-        <v>-14.89416506666666</v>
+        <v>-15.18797186666666</v>
       </c>
       <c r="Q90">
-        <v>-11.95416506666666</v>
+        <v>-12.24797186666666</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4664859506322381</v>
+        <v>0.5047301279624415</v>
       </c>
       <c r="T90">
-        <v>8.199952200170463</v>
+        <v>8.945402400185959</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05299184882821988</v>
+        <v>0.05239643479644213</v>
       </c>
       <c r="W90">
-        <v>0.2233045220463058</v>
+        <v>0.2234449206749989</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.423934790625759</v>
+        <v>0.419171478371537</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2543862934766176</v>
+        <v>0.2562862934766176</v>
       </c>
       <c r="C91">
-        <v>-78.30809106644864</v>
+        <v>-80.0166845474983</v>
       </c>
       <c r="D91">
-        <v>31.52790893355134</v>
+        <v>31.2433154525017</v>
       </c>
       <c r="E91">
-        <v>85.43599999999998</v>
+        <v>86.86000000000001</v>
       </c>
       <c r="F91">
-        <v>126.736</v>
+        <v>128.16</v>
       </c>
       <c r="G91">
         <v>16.9</v>
@@ -8877,37 +8877,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M91">
-        <v>29.88434879999999</v>
+        <v>30.220128</v>
       </c>
       <c r="N91">
-        <v>-17.35768213333333</v>
+        <v>-17.69346133333333</v>
       </c>
       <c r="O91">
-        <v>-2.169710266666666</v>
+        <v>-2.211682666666666</v>
       </c>
       <c r="P91">
-        <v>-15.18797186666666</v>
+        <v>-15.48177866666667</v>
       </c>
       <c r="Q91">
-        <v>-12.24797186666666</v>
+        <v>-12.54177866666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5047301279624415</v>
+        <v>0.5506231407586857</v>
       </c>
       <c r="T91">
-        <v>8.945402400185959</v>
+        <v>9.839942640204557</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05239643479644213</v>
+        <v>0.05181425218759277</v>
       </c>
       <c r="W91">
-        <v>0.2234449206749989</v>
+        <v>0.2235821993341656</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.419171478371537</v>
+        <v>0.4145140175007421</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2562862934766176</v>
+        <v>0.2581862934766176</v>
       </c>
       <c r="C92">
-        <v>-80.0166845474983</v>
+        <v>-81.72018610283894</v>
       </c>
       <c r="D92">
-        <v>31.2433154525017</v>
+        <v>30.96381389716103</v>
       </c>
       <c r="E92">
-        <v>86.86000000000001</v>
+        <v>88.28399999999999</v>
       </c>
       <c r="F92">
-        <v>128.16</v>
+        <v>129.584</v>
       </c>
       <c r="G92">
         <v>16.9</v>
@@ -8959,37 +8959,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M92">
-        <v>30.220128</v>
+        <v>30.5559072</v>
       </c>
       <c r="N92">
-        <v>-17.69346133333333</v>
+        <v>-18.02924053333333</v>
       </c>
       <c r="O92">
-        <v>-2.211682666666666</v>
+        <v>-2.253655066666666</v>
       </c>
       <c r="P92">
-        <v>-15.48177866666667</v>
+        <v>-15.77558546666666</v>
       </c>
       <c r="Q92">
-        <v>-12.54177866666667</v>
+        <v>-12.83558546666666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5506231407586857</v>
+        <v>0.6067146008429841</v>
       </c>
       <c r="T92">
-        <v>9.839942640204557</v>
+        <v>10.93326960022729</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05181425218759277</v>
+        <v>0.05124486480091593</v>
       </c>
       <c r="W92">
-        <v>0.2235821993341656</v>
+        <v>0.223716460879944</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4145140175007421</v>
+        <v>0.4099589184073275</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2581862934766176</v>
+        <v>0.2600862934766177</v>
       </c>
       <c r="C93">
-        <v>-81.72018610283894</v>
+        <v>-83.41873117732841</v>
       </c>
       <c r="D93">
-        <v>30.96381389716103</v>
+        <v>30.68926882267158</v>
       </c>
       <c r="E93">
-        <v>88.28399999999999</v>
+        <v>89.708</v>
       </c>
       <c r="F93">
-        <v>129.584</v>
+        <v>131.008</v>
       </c>
       <c r="G93">
         <v>16.9</v>
@@ -9041,37 +9041,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M93">
-        <v>30.5559072</v>
+        <v>30.8916864</v>
       </c>
       <c r="N93">
-        <v>-18.02924053333333</v>
+        <v>-18.36501973333333</v>
       </c>
       <c r="O93">
-        <v>-2.253655066666666</v>
+        <v>-2.295627466666666</v>
       </c>
       <c r="P93">
-        <v>-15.77558546666666</v>
+        <v>-16.06939226666666</v>
       </c>
       <c r="Q93">
-        <v>-12.83558546666666</v>
+        <v>-13.12939226666666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6067146008429841</v>
+        <v>0.6768289259483574</v>
       </c>
       <c r="T93">
-        <v>10.93326960022729</v>
+        <v>12.2999283002557</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05124486480091593</v>
+        <v>0.05068785540090597</v>
       </c>
       <c r="W93">
-        <v>0.223716460879944</v>
+        <v>0.2238478036964664</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4099589184073275</v>
+        <v>0.4055028432072477</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2600862934766177</v>
+        <v>0.2619862934766177</v>
       </c>
       <c r="C94">
-        <v>-83.41873117732841</v>
+        <v>-85.1124504542787</v>
       </c>
       <c r="D94">
-        <v>30.68926882267158</v>
+        <v>30.41954954572129</v>
       </c>
       <c r="E94">
-        <v>89.708</v>
+        <v>91.13200000000001</v>
       </c>
       <c r="F94">
-        <v>131.008</v>
+        <v>132.432</v>
       </c>
       <c r="G94">
         <v>16.9</v>
@@ -9123,37 +9123,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M94">
-        <v>30.8916864</v>
+        <v>31.2274656</v>
       </c>
       <c r="N94">
-        <v>-18.36501973333333</v>
+        <v>-18.70079893333333</v>
       </c>
       <c r="O94">
-        <v>-2.295627466666666</v>
+        <v>-2.337599866666666</v>
       </c>
       <c r="P94">
-        <v>-16.06939226666666</v>
+        <v>-16.36319906666667</v>
       </c>
       <c r="Q94">
-        <v>-13.12939226666666</v>
+        <v>-13.42319906666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6768289259483574</v>
+        <v>0.7669759153695513</v>
       </c>
       <c r="T94">
-        <v>12.2999283002557</v>
+        <v>14.05706091457794</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05068785540090597</v>
+        <v>0.05014282469767042</v>
       </c>
       <c r="W94">
-        <v>0.2238478036964664</v>
+        <v>0.2239763219362893</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4055028432072477</v>
+        <v>0.4011425975813634</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2619862934766177</v>
+        <v>0.2638862934766176</v>
       </c>
       <c r="C95">
-        <v>-85.1124504542787</v>
+        <v>-86.80147006287262</v>
       </c>
       <c r="D95">
-        <v>30.41954954572129</v>
+        <v>30.15452993712738</v>
       </c>
       <c r="E95">
-        <v>91.13200000000001</v>
+        <v>92.55600000000001</v>
       </c>
       <c r="F95">
-        <v>132.432</v>
+        <v>133.856</v>
       </c>
       <c r="G95">
         <v>16.9</v>
@@ -9205,37 +9205,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M95">
-        <v>31.2274656</v>
+        <v>31.5632448</v>
       </c>
       <c r="N95">
-        <v>-18.70079893333333</v>
+        <v>-19.03657813333333</v>
       </c>
       <c r="O95">
-        <v>-2.337599866666666</v>
+        <v>-2.379572266666667</v>
       </c>
       <c r="P95">
-        <v>-16.36319906666667</v>
+        <v>-16.65700586666667</v>
       </c>
       <c r="Q95">
-        <v>-13.42319906666667</v>
+        <v>-13.71700586666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7669759153695513</v>
+        <v>0.8871719012644769</v>
       </c>
       <c r="T95">
-        <v>14.05706091457794</v>
+        <v>16.39990440034094</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05014282469767042</v>
+        <v>0.04960939039237605</v>
       </c>
       <c r="W95">
-        <v>0.2239763219362893</v>
+        <v>0.2241021057454778</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4011425975813634</v>
+        <v>0.3968751231390084</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2638862934766176</v>
+        <v>0.2657862934766176</v>
       </c>
       <c r="C96">
-        <v>-86.80147006287262</v>
+        <v>-88.48591177483151</v>
       </c>
       <c r="D96">
-        <v>30.15452993712738</v>
+        <v>29.8940882251685</v>
       </c>
       <c r="E96">
-        <v>92.55600000000001</v>
+        <v>93.98000000000002</v>
       </c>
       <c r="F96">
-        <v>133.856</v>
+        <v>135.28</v>
       </c>
       <c r="G96">
         <v>16.9</v>
@@ -9287,37 +9287,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M96">
-        <v>31.5632448</v>
+        <v>31.899024</v>
       </c>
       <c r="N96">
-        <v>-19.03657813333333</v>
+        <v>-19.37235733333333</v>
       </c>
       <c r="O96">
-        <v>-2.379572266666667</v>
+        <v>-2.421544666666667</v>
       </c>
       <c r="P96">
-        <v>-16.65700586666667</v>
+        <v>-16.95081266666667</v>
       </c>
       <c r="Q96">
-        <v>-13.71700586666667</v>
+        <v>-14.01081266666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8871719012644769</v>
+        <v>1.055446281517373</v>
       </c>
       <c r="T96">
-        <v>16.39990440034094</v>
+        <v>19.67988528040914</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04960939039237605</v>
+        <v>0.04908718628298262</v>
       </c>
       <c r="W96">
-        <v>0.2241021057454778</v>
+        <v>0.2242252414744727</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3968751231390084</v>
+        <v>0.3926974902638609</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2657862934766176</v>
+        <v>0.2676862934766177</v>
       </c>
       <c r="C97">
-        <v>-88.48591177483151</v>
+        <v>-90.16589319097879</v>
       </c>
       <c r="D97">
-        <v>29.8940882251685</v>
+        <v>29.63810680902119</v>
       </c>
       <c r="E97">
-        <v>93.98000000000002</v>
+        <v>95.404</v>
       </c>
       <c r="F97">
-        <v>135.28</v>
+        <v>136.704</v>
       </c>
       <c r="G97">
         <v>16.9</v>
@@ -9369,37 +9369,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M97">
-        <v>31.899024</v>
+        <v>32.23480319999999</v>
       </c>
       <c r="N97">
-        <v>-19.37235733333333</v>
+        <v>-19.70813653333333</v>
       </c>
       <c r="O97">
-        <v>-2.421544666666667</v>
+        <v>-2.463517066666666</v>
       </c>
       <c r="P97">
-        <v>-16.95081266666667</v>
+        <v>-17.24461946666666</v>
       </c>
       <c r="Q97">
-        <v>-14.01081266666667</v>
+        <v>-14.30461946666666</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.055446281517373</v>
+        <v>1.307857851896717</v>
       </c>
       <c r="T97">
-        <v>19.67988528040914</v>
+        <v>24.59985660051143</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04908718628298262</v>
+        <v>0.04857586142586823</v>
       </c>
       <c r="W97">
-        <v>0.2242252414744727</v>
+        <v>0.2243458118757803</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3926974902638609</v>
+        <v>0.3886068914069458</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2676862934766177</v>
+        <v>0.2695862934766177</v>
       </c>
       <c r="C98">
-        <v>-90.16589319097879</v>
+        <v>-91.84152791829968</v>
       </c>
       <c r="D98">
-        <v>29.63810680902119</v>
+        <v>29.3864720817003</v>
       </c>
       <c r="E98">
-        <v>95.404</v>
+        <v>96.828</v>
       </c>
       <c r="F98">
-        <v>136.704</v>
+        <v>138.128</v>
       </c>
       <c r="G98">
         <v>16.9</v>
@@ -9451,37 +9451,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M98">
-        <v>32.23480319999999</v>
+        <v>32.5705824</v>
       </c>
       <c r="N98">
-        <v>-19.70813653333333</v>
+        <v>-20.04391573333333</v>
       </c>
       <c r="O98">
-        <v>-2.463517066666666</v>
+        <v>-2.505489466666666</v>
       </c>
       <c r="P98">
-        <v>-17.24461946666666</v>
+        <v>-17.53842626666667</v>
       </c>
       <c r="Q98">
-        <v>-14.30461946666666</v>
+        <v>-14.59842626666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.307857851896713</v>
+        <v>1.728543802528951</v>
       </c>
       <c r="T98">
-        <v>24.59985660051137</v>
+        <v>32.79980880068182</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04857586142586823</v>
+        <v>0.04807507934931288</v>
       </c>
       <c r="W98">
-        <v>0.2243458118757803</v>
+        <v>0.224463896289432</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3886068914069458</v>
+        <v>0.384600634794503</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2695862934766177</v>
+        <v>0.2714862934766176</v>
       </c>
       <c r="C99">
-        <v>-91.84152791829968</v>
+        <v>-93.51292573805699</v>
       </c>
       <c r="D99">
-        <v>29.3864720817003</v>
+        <v>29.13907426194297</v>
       </c>
       <c r="E99">
-        <v>96.828</v>
+        <v>98.25199999999998</v>
       </c>
       <c r="F99">
-        <v>138.128</v>
+        <v>139.552</v>
       </c>
       <c r="G99">
         <v>16.9</v>
@@ -9533,37 +9533,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M99">
-        <v>32.5705824</v>
+        <v>32.90636159999999</v>
       </c>
       <c r="N99">
-        <v>-20.04391573333333</v>
+        <v>-20.37969493333332</v>
       </c>
       <c r="O99">
-        <v>-2.505489466666666</v>
+        <v>-2.547461866666665</v>
       </c>
       <c r="P99">
-        <v>-17.53842626666667</v>
+        <v>-17.83223306666666</v>
       </c>
       <c r="Q99">
-        <v>-14.59842626666667</v>
+        <v>-14.89223306666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.728543802528951</v>
+        <v>2.569915703793426</v>
       </c>
       <c r="T99">
-        <v>32.79980880068182</v>
+        <v>49.19971320102273</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04807507934931288</v>
+        <v>0.04758451731513623</v>
       </c>
       <c r="W99">
-        <v>0.224463896289432</v>
+        <v>0.2245795708170909</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.384600634794503</v>
+        <v>0.3806761385210898</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2714862934766176</v>
+        <v>0.2733862934766176</v>
       </c>
       <c r="C100">
-        <v>-93.51292573805699</v>
+        <v>-95.18019276548623</v>
       </c>
       <c r="D100">
-        <v>29.13907426194297</v>
+        <v>28.89580723451374</v>
       </c>
       <c r="E100">
-        <v>98.25199999999998</v>
+        <v>99.67599999999999</v>
       </c>
       <c r="F100">
-        <v>139.552</v>
+        <v>140.976</v>
       </c>
       <c r="G100">
         <v>16.9</v>
@@ -9615,37 +9615,37 @@
         <v>12.52666666666667</v>
       </c>
       <c r="M100">
-        <v>32.90636159999999</v>
+        <v>33.24214079999999</v>
       </c>
       <c r="N100">
-        <v>-20.37969493333332</v>
+        <v>-20.71547413333333</v>
       </c>
       <c r="O100">
-        <v>-2.547461866666665</v>
+        <v>-2.589434266666666</v>
       </c>
       <c r="P100">
-        <v>-17.83223306666666</v>
+        <v>-18.12603986666666</v>
       </c>
       <c r="Q100">
-        <v>-14.89223306666666</v>
+        <v>-15.18603986666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.569915703793426</v>
+        <v>5.094031407586852</v>
       </c>
       <c r="T100">
-        <v>49.19971320102273</v>
+        <v>98.39942640204545</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04758451731513623</v>
+        <v>0.04710386562508434</v>
       </c>
       <c r="W100">
-        <v>0.2245795708170909</v>
+        <v>0.2246929084856051</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3806761385210898</v>
+        <v>0.3768309250006747</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2733862934766176</v>
-      </c>
-      <c r="C101">
-        <v>-95.18019276548623</v>
-      </c>
-      <c r="D101">
-        <v>28.89580723451374</v>
-      </c>
-      <c r="E101">
-        <v>99.67599999999999</v>
-      </c>
-      <c r="F101">
-        <v>140.976</v>
-      </c>
-      <c r="G101">
-        <v>16.9</v>
-      </c>
-      <c r="H101">
-        <v>101.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>15.46666666666667</v>
-      </c>
-      <c r="K101">
-        <v>2.94</v>
-      </c>
-      <c r="L101">
-        <v>12.52666666666667</v>
-      </c>
-      <c r="M101">
-        <v>33.24214079999999</v>
-      </c>
-      <c r="N101">
-        <v>-20.71547413333333</v>
-      </c>
-      <c r="O101">
-        <v>-2.589434266666666</v>
-      </c>
-      <c r="P101">
-        <v>-18.12603986666666</v>
-      </c>
-      <c r="Q101">
-        <v>-15.18603986666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.094031407586852</v>
-      </c>
-      <c r="T101">
-        <v>98.39942640204545</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04710386562508434</v>
-      </c>
-      <c r="W101">
-        <v>0.2246929084856051</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3768309250006747</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
